--- a/model/GRG_model_v0.3.xlsx
+++ b/model/GRG_model_v0.3.xlsx
@@ -126,7 +126,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">FY21: AR21 says 'we currently have ... 375 franchise locations' (written in early 2022), so treat as approximate. FY25: not stated in the report text. Find it in the FY25 results announcement (March 2026) and type it in.</t>
+          <t xml:space="preserve">FY21: AR21 says 'we currently have ... 375 franchise locations' (written in early 2022), so treat as approximate. FY25: 602 franchised and 2,137 company-managed, from the Q4 trading update (8 Jan 2026).</t>
         </r>
       </text>
     </comment>
@@ -138,7 +138,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Includes franchised openings (FY22: 70; FY23: 72; FY24: 63). FY25 gross openings and closures are not stated in the report text; only 121 net. Find them in the FY25 results announcement.</t>
+          <t xml:space="preserve">Includes franchised openings (FY22: 70; FY23: 72; FY24: 63). FY25: 207 opened and 86 closed (50 relocations, 36 closures), from the Q4 trading update (8 Jan 2026).</t>
         </r>
       </text>
     </comment>
@@ -250,18 +250,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="G41" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">ESTIMATE, not from the annual report. Derived from the 12 May 2026 trading update (2,141 company-managed and 618 franchised shops at 9 May 2026, after 20 net openings in 2026) by assuming 60% of those openings were company-managed: 618 - 8 = 610. Replace with the actual figure from the FY25 results announcement.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -735,7 +723,7 @@
     <t xml:space="preserve">of which franchised</t>
   </si>
   <si>
-    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 AR23 p17; FY24 AR24 p33; FY25 not found</t>
+    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 AR23 p17; FY24 AR24 p33; FY25 Q4 trading update 8 Jan 2026</t>
   </si>
   <si>
     <t xml:space="preserve">of which company-managed</t>
@@ -744,13 +732,13 @@
     <t xml:space="preserve">Gross openings</t>
   </si>
   <si>
-    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 AR23 p17; FY24 AR24 p22; FY25 not found</t>
+    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 AR23 p17; FY24 AR24 p22; FY25 Q4 trading update 8 Jan 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Closures (incl. relocations)</t>
   </si>
   <si>
-    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 derived; FY24 AR24 p22</t>
+    <t xml:space="preserve">FY21 AR21 p18; FY22 AR22 p15; FY23 derived; FY24 AR24 p22; FY25 Q4 trading update</t>
   </si>
   <si>
     <t xml:space="preserve">Net openings</t>
@@ -2064,7 +2052,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2092,12 +2080,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
@@ -2143,7 +2125,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2268,14 +2250,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2357,6 +2331,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2458,7 +2436,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -3233,42 +3211,42 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="43" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="43" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="43" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="43" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="43" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="43" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="43" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="43" t="s">
         <v>539</v>
       </c>
     </row>
@@ -4110,8 +4088,8 @@
       <c r="F41" s="29" t="n">
         <v>561</v>
       </c>
-      <c r="G41" s="31" t="n">
-        <v>610</v>
+      <c r="G41" s="29" t="n">
+        <v>602</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4139,7 +4117,7 @@
       </c>
       <c r="G42" s="30" t="n">
         <f aca="false">IF(G41="","",G40-G41)</f>
-        <v>2129</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4161,7 +4139,9 @@
       <c r="F43" s="29" t="n">
         <v>226</v>
       </c>
-      <c r="G43" s="32"/>
+      <c r="G43" s="29" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
@@ -4182,7 +4162,9 @@
       <c r="F44" s="29" t="n">
         <v>-81</v>
       </c>
-      <c r="G44" s="32"/>
+      <c r="G44" s="29" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
@@ -4247,19 +4229,19 @@
       <c r="B47" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="33" t="n">
+      <c r="C47" s="31" t="n">
         <v>0.524</v>
       </c>
-      <c r="D47" s="33" t="n">
+      <c r="D47" s="31" t="n">
         <v>0.178</v>
       </c>
-      <c r="E47" s="33" t="n">
+      <c r="E47" s="31" t="n">
         <v>0.137</v>
       </c>
-      <c r="F47" s="33" t="n">
+      <c r="F47" s="31" t="n">
         <v>0.055</v>
       </c>
-      <c r="G47" s="33" t="n">
+      <c r="G47" s="31" t="n">
         <v>0.024</v>
       </c>
     </row>
@@ -4270,15 +4252,15 @@
       <c r="B48" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="33" t="n">
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="31" t="n">
         <v>0.149</v>
       </c>
-      <c r="F48" s="33" t="n">
+      <c r="F48" s="31" t="n">
         <v>0.074</v>
       </c>
-      <c r="G48" s="33" t="n">
+      <c r="G48" s="31" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -4289,25 +4271,25 @@
       <c r="B49" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="35" t="n">
+      <c r="C49" s="33" t="n">
         <f aca="false">IF(C42="","",C36/C42)</f>
         <v>0.608084163898117</v>
       </c>
-      <c r="D49" s="35" t="n">
+      <c r="D49" s="33" t="n">
         <f aca="false">IF(D42="","",D36/AVERAGE(D42,IF(C42="",D42,C42)))</f>
         <v>0.732358516111562</v>
       </c>
-      <c r="E49" s="35" t="n">
+      <c r="E49" s="33" t="n">
         <f aca="false">IF(E42="","",E36/AVERAGE(E42,IF(D42="",E42,D42)))</f>
         <v>0.835312418978481</v>
       </c>
-      <c r="F49" s="35" t="n">
+      <c r="F49" s="33" t="n">
         <f aca="false">IF(F42="","",F36/AVERAGE(F42,IF(E42="",F42,E42)))</f>
         <v>0.884877079711944</v>
       </c>
-      <c r="G49" s="35" t="n">
+      <c r="G49" s="33" t="n">
         <f aca="false">IF(G42="","",G36/AVERAGE(G42,IF(F42="",G42,F42)))</f>
-        <v>0.906450071667463</v>
+        <v>0.904721030042919</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6345,22 +6327,22 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="34" t="s">
         <v>239</v>
       </c>
     </row>
@@ -6381,9 +6363,9 @@
       <c r="B6" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
@@ -6392,13 +6374,13 @@
       <c r="B7" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="36" t="n">
         <f aca="false">Historical!G42-Historical!F42</f>
-        <v>72</v>
-      </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+        <v>80</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
@@ -6407,13 +6389,13 @@
       <c r="B8" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="36" t="n">
         <f aca="false">Historical!G42</f>
-        <v>2129</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+        <v>2137</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
@@ -6432,13 +6414,13 @@
       <c r="B10" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="39" t="n">
+      <c r="C10" s="37" t="n">
         <f aca="false">Historical!G47</f>
         <v>0.024</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
@@ -6447,13 +6429,13 @@
       <c r="B11" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="C11" s="41" t="n">
+      <c r="C11" s="39" t="n">
         <f aca="false">Historical!G49</f>
-        <v>0.906450071667463</v>
-      </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+        <v>0.904721030042919</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
@@ -6462,9 +6444,9 @@
       <c r="B12" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
@@ -6483,9 +6465,9 @@
       <c r="B14" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
@@ -6494,9 +6476,9 @@
       <c r="B15" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
@@ -6505,9 +6487,9 @@
       <c r="B16" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
@@ -6516,13 +6498,13 @@
       <c r="B17" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="42" t="n">
         <f aca="false">Historical!G36</f>
         <v>1897.2</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
@@ -6531,13 +6513,13 @@
       <c r="B18" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="42" t="n">
         <f aca="false">Historical!G37</f>
         <v>254</v>
       </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
@@ -6546,13 +6528,13 @@
       <c r="B19" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="42" t="n">
         <f aca="false">Historical!G7</f>
         <v>2151.2</v>
       </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
@@ -6561,9 +6543,9 @@
       <c r="B20" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
@@ -6596,7 +6578,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="43" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6607,7 +6589,7 @@
       <c r="B25" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="31" t="n">
         <v>0.072</v>
       </c>
     </row>
@@ -6723,23 +6705,23 @@
       <c r="B7" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="42" t="n">
         <f aca="false">Historical!C7</f>
         <v>1229.7</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="42" t="n">
         <f aca="false">Historical!D7</f>
         <v>1512.8</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="42" t="n">
         <f aca="false">Historical!E7</f>
         <v>1809.6</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="42" t="n">
         <f aca="false">Historical!F7</f>
         <v>2014.4</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">Historical!G7</f>
         <v>2151.2</v>
       </c>
@@ -6760,23 +6742,23 @@
       <c r="A8" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="42" t="n">
         <f aca="false">Historical!C8</f>
         <v>-447.7</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="42" t="n">
         <f aca="false">Historical!D8</f>
         <v>-574.5</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="42" t="n">
         <f aca="false">Historical!E8</f>
         <v>-710.5</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="42" t="n">
         <f aca="false">Historical!F8</f>
         <v>-770.8</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">Historical!G8</f>
         <v>-829.1</v>
       </c>
@@ -6797,35 +6779,35 @@
       <c r="A9" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="42" t="n">
         <f aca="false">Historical!C9</f>
         <v>782</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="42" t="n">
         <f aca="false">Historical!D9</f>
         <v>938.3</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="42" t="n">
         <f aca="false">Historical!E9</f>
         <v>1099.1</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="42" t="n">
         <f aca="false">Historical!F9</f>
         <v>1243.6</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">Historical!G9</f>
         <v>1322.1</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="44" t="n">
         <f aca="false">H7+H8</f>
         <v>0</v>
       </c>
-      <c r="I9" s="46" t="n">
+      <c r="I9" s="44" t="n">
         <f aca="false">I7+I8</f>
         <v>0</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="44" t="n">
         <f aca="false">J7+J8</f>
         <v>0</v>
       </c>
@@ -6834,23 +6816,23 @@
       <c r="A10" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="42" t="n">
         <f aca="false">Historical!C10</f>
         <v>-567.6</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="42" t="n">
         <f aca="false">Historical!D10</f>
         <v>-713.2</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="42" t="n">
         <f aca="false">Historical!E10</f>
         <v>-844.2</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="42" t="n">
         <f aca="false">Historical!F10</f>
         <v>-950.1</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">Historical!G10</f>
         <v>-1036.3</v>
       </c>
@@ -6871,23 +6853,23 @@
       <c r="A11" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="42" t="n">
         <f aca="false">Historical!C11</f>
         <v>-61.2</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="42" t="n">
         <f aca="false">Historical!D11</f>
         <v>-70.7</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="42" t="n">
         <f aca="false">Historical!E11</f>
         <v>-82.9</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="42" t="n">
         <f aca="false">Historical!F11</f>
         <v>-97.9</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">Historical!G11</f>
         <v>-102.1</v>
       </c>
@@ -6908,23 +6890,23 @@
       <c r="A12" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="42" t="n">
         <f aca="false">Historical!C12</f>
         <v>0</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="42" t="n">
         <f aca="false">Historical!D12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="42" t="n">
         <f aca="false">Historical!E12</f>
         <v>20.3</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="42" t="n">
         <f aca="false">Historical!F12</f>
         <v>13.8</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">Historical!G12</f>
         <v>0</v>
       </c>
@@ -6945,35 +6927,35 @@
       <c r="A13" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="44" t="n">
+      <c r="C13" s="42" t="n">
         <f aca="false">Historical!C13</f>
         <v>153.2</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="42" t="n">
         <f aca="false">Historical!D13</f>
         <v>154.4</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="42" t="n">
         <f aca="false">Historical!E13</f>
         <v>192.3</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="42" t="n">
         <f aca="false">Historical!F13</f>
         <v>209.4</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">Historical!G13</f>
         <v>183.7</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="44" t="n">
         <f aca="false">H9+H10+H11+H12</f>
         <v>-45</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="44" t="n">
         <f aca="false">I9+I10+I11+I12</f>
         <v>-10</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="44" t="n">
         <f aca="false">J9+J10+J11+J12</f>
         <v>-5</v>
       </c>
@@ -6982,23 +6964,23 @@
       <c r="A14" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="42" t="n">
         <f aca="false">Historical!C14</f>
         <v>0</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="42" t="n">
         <f aca="false">Historical!D14</f>
         <v>1.4</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="42" t="n">
         <f aca="false">Historical!E14</f>
         <v>6.1</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="42" t="n">
         <f aca="false">Historical!F14</f>
         <v>8.1</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="42" t="n">
         <f aca="false">Historical!G14</f>
         <v>1.8</v>
       </c>
@@ -7019,23 +7001,23 @@
       <c r="A15" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="42" t="n">
         <f aca="false">Historical!C15</f>
         <v>-7.6</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="42" t="n">
         <f aca="false">Historical!D15</f>
         <v>-7.5</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="42" t="n">
         <f aca="false">Historical!E15</f>
         <v>-10.1</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="42" t="n">
         <f aca="false">Historical!F15</f>
         <v>-13.6</v>
       </c>
-      <c r="G15" s="44" t="n">
+      <c r="G15" s="42" t="n">
         <f aca="false">Historical!G15</f>
         <v>-18.1</v>
       </c>
@@ -7045,48 +7027,48 @@
       </c>
       <c r="I15" s="28" t="n">
         <f aca="false">-I150-I151</f>
-        <v>-19.3112975105683</v>
+        <v>-19.3093542349088</v>
       </c>
       <c r="J15" s="28" t="n">
         <f aca="false">-J150-J151</f>
-        <v>-19.8551139502114</v>
+        <v>-19.851134861956</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C16" s="42" t="n">
         <f aca="false">Historical!C16</f>
         <v>145.6</v>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="42" t="n">
         <f aca="false">Historical!D16</f>
         <v>148.3</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="42" t="n">
         <f aca="false">Historical!E16</f>
         <v>188.3</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="42" t="n">
         <f aca="false">Historical!F16</f>
         <v>203.9</v>
       </c>
-      <c r="G16" s="44" t="n">
+      <c r="G16" s="42" t="n">
         <f aca="false">Historical!G16</f>
         <v>167.4</v>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="44" t="n">
         <f aca="false">H13+H14+H15</f>
         <v>-61.6682</v>
       </c>
-      <c r="I16" s="46" t="n">
+      <c r="I16" s="44" t="n">
         <f aca="false">I13+I14+I15</f>
-        <v>-29.3112975105683</v>
-      </c>
-      <c r="J16" s="46" t="n">
+        <v>-29.3093542349088</v>
+      </c>
+      <c r="J16" s="44" t="n">
         <f aca="false">J13+J14+J15</f>
-        <v>-24.8551139502114</v>
+        <v>-24.851134861956</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7096,23 +7078,23 @@
       <c r="B17" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="42" t="n">
         <f aca="false">Historical!C17</f>
         <v>-28.1</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="42" t="n">
         <f aca="false">Historical!D17</f>
         <v>-28</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="42" t="n">
         <f aca="false">Historical!E17</f>
         <v>-45.8</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="42" t="n">
         <f aca="false">Historical!F17</f>
         <v>-50.5</v>
       </c>
-      <c r="G17" s="44" t="n">
+      <c r="G17" s="42" t="n">
         <f aca="false">Historical!G17</f>
         <v>-45.2</v>
       </c>
@@ -7122,48 +7104,48 @@
       </c>
       <c r="I17" s="28" t="n">
         <f aca="false">-Drivers!$D$18*I16</f>
-        <v>7.62093735274777</v>
+        <v>7.62043210107628</v>
       </c>
       <c r="J17" s="28" t="n">
         <f aca="false">-Drivers!$E$18*J16</f>
-        <v>6.46232962705496</v>
+        <v>6.46129506410856</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="42" t="n">
         <f aca="false">Historical!C18</f>
         <v>117.5</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="42" t="n">
         <f aca="false">Historical!D18</f>
         <v>120.3</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="42" t="n">
         <f aca="false">Historical!E18</f>
         <v>142.5</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="42" t="n">
         <f aca="false">Historical!F18</f>
         <v>153.4</v>
       </c>
-      <c r="G18" s="44" t="n">
+      <c r="G18" s="42" t="n">
         <f aca="false">Historical!G18</f>
         <v>122.2</v>
       </c>
-      <c r="H18" s="46" t="n">
+      <c r="H18" s="44" t="n">
         <f aca="false">H16+H17</f>
         <v>-45.634468</v>
       </c>
-      <c r="I18" s="46" t="n">
+      <c r="I18" s="44" t="n">
         <f aca="false">I16+I17</f>
-        <v>-21.6903601578206</v>
-      </c>
-      <c r="J18" s="46" t="n">
+        <v>-21.6889221338325</v>
+      </c>
+      <c r="J18" s="44" t="n">
         <f aca="false">J16+J17</f>
-        <v>-18.3927843231564</v>
+        <v>-18.3898397978475</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7187,23 +7169,23 @@
       <c r="B21" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C21" s="44" t="n">
+      <c r="C21" s="42" t="n">
         <f aca="false">Historical!C21</f>
         <v>0</v>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="42" t="n">
         <f aca="false">Historical!D21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="44" t="n">
+      <c r="E21" s="42" t="n">
         <f aca="false">Historical!E21</f>
         <v>20.6</v>
       </c>
-      <c r="F21" s="44" t="n">
+      <c r="F21" s="42" t="n">
         <f aca="false">Historical!F21</f>
         <v>14.1</v>
       </c>
-      <c r="G21" s="44" t="n">
+      <c r="G21" s="42" t="n">
         <f aca="false">Historical!G21</f>
         <v>-3.8</v>
       </c>
@@ -7224,23 +7206,23 @@
       <c r="A22" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="44" t="n">
+      <c r="C22" s="42" t="n">
         <f aca="false">Historical!C22</f>
         <v>0</v>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="42" t="n">
         <f aca="false">Historical!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="42" t="n">
         <f aca="false">Historical!E22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="44" t="n">
+      <c r="F22" s="42" t="n">
         <f aca="false">Historical!F22</f>
         <v>0</v>
       </c>
-      <c r="G22" s="44" t="n">
+      <c r="G22" s="42" t="n">
         <f aca="false">Historical!G22</f>
         <v>-0.7</v>
       </c>
@@ -7261,23 +7243,23 @@
       <c r="A23" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="42" t="n">
         <f aca="false">Historical!C23</f>
         <v>0</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="42" t="n">
         <f aca="false">Historical!D23</f>
         <v>0</v>
       </c>
-      <c r="E23" s="44" t="n">
+      <c r="E23" s="42" t="n">
         <f aca="false">Historical!E23</f>
         <v>-4.8</v>
       </c>
-      <c r="F23" s="44" t="n">
+      <c r="F23" s="42" t="n">
         <f aca="false">Historical!F23</f>
         <v>-1.7</v>
       </c>
-      <c r="G23" s="44" t="n">
+      <c r="G23" s="42" t="n">
         <f aca="false">Historical!G23</f>
         <v>0.9</v>
       </c>
@@ -7301,35 +7283,35 @@
       <c r="B24" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="C24" s="44" t="n">
+      <c r="C24" s="42" t="n">
         <f aca="false">Historical!C24</f>
         <v>153.2</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="42" t="n">
         <f aca="false">Historical!D24</f>
         <v>154.4</v>
       </c>
-      <c r="E24" s="44" t="n">
+      <c r="E24" s="42" t="n">
         <f aca="false">Historical!E24</f>
         <v>171.7</v>
       </c>
-      <c r="F24" s="44" t="n">
+      <c r="F24" s="42" t="n">
         <f aca="false">Historical!F24</f>
         <v>195.3</v>
       </c>
-      <c r="G24" s="44" t="n">
+      <c r="G24" s="42" t="n">
         <f aca="false">Historical!G24</f>
         <v>187.5</v>
       </c>
-      <c r="H24" s="46" t="n">
+      <c r="H24" s="44" t="n">
         <f aca="false">H13-H21</f>
         <v>0</v>
       </c>
-      <c r="I24" s="46" t="n">
+      <c r="I24" s="44" t="n">
         <f aca="false">I13-I21</f>
         <v>0</v>
       </c>
-      <c r="J24" s="46" t="n">
+      <c r="J24" s="44" t="n">
         <f aca="false">J13-J21</f>
         <v>0</v>
       </c>
@@ -7338,60 +7320,60 @@
       <c r="A25" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="44" t="n">
+      <c r="C25" s="42" t="n">
         <f aca="false">Historical!C25</f>
         <v>145.6</v>
       </c>
-      <c r="D25" s="44" t="n">
+      <c r="D25" s="42" t="n">
         <f aca="false">Historical!D25</f>
         <v>148.3</v>
       </c>
-      <c r="E25" s="44" t="n">
+      <c r="E25" s="42" t="n">
         <f aca="false">Historical!E25</f>
         <v>167.7</v>
       </c>
-      <c r="F25" s="44" t="n">
+      <c r="F25" s="42" t="n">
         <f aca="false">Historical!F25</f>
         <v>189.8</v>
       </c>
-      <c r="G25" s="44" t="n">
+      <c r="G25" s="42" t="n">
         <f aca="false">Historical!G25</f>
         <v>171.9</v>
       </c>
-      <c r="H25" s="46" t="n">
+      <c r="H25" s="44" t="n">
         <f aca="false">H16-H21-H22</f>
         <v>-16.6682</v>
       </c>
-      <c r="I25" s="46" t="n">
+      <c r="I25" s="44" t="n">
         <f aca="false">I16-I21-I22</f>
-        <v>-19.3112975105683</v>
-      </c>
-      <c r="J25" s="46" t="n">
+        <v>-19.3093542349088</v>
+      </c>
+      <c r="J25" s="44" t="n">
         <f aca="false">J16-J21-J22</f>
-        <v>-19.8551139502114</v>
+        <v>-19.851134861956</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="37" t="n">
         <f aca="false">Historical!C26</f>
         <v>0.124583231682524</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="37" t="n">
         <f aca="false">Historical!D26</f>
         <v>0.102062400846113</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="37" t="n">
         <f aca="false">Historical!E26</f>
         <v>0.0948828470380194</v>
       </c>
-      <c r="F26" s="39" t="n">
+      <c r="F26" s="37" t="n">
         <f aca="false">Historical!F26</f>
         <v>0.0969519459888801</v>
       </c>
-      <c r="G26" s="39" t="n">
+      <c r="G26" s="37" t="n">
         <f aca="false">Historical!G26</f>
         <v>0.0871606545184083</v>
       </c>
@@ -7412,23 +7394,23 @@
       <c r="A27" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="37" t="n">
         <f aca="false">Historical!C27</f>
         <v>0.192994505494506</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D27" s="37" t="n">
         <f aca="false">Historical!D27</f>
         <v>0.188806473364801</v>
       </c>
-      <c r="E27" s="39" t="n">
+      <c r="E27" s="37" t="n">
         <f aca="false">Historical!E27</f>
         <v>0.243228890069039</v>
       </c>
-      <c r="F27" s="39" t="n">
+      <c r="F27" s="37" t="n">
         <f aca="false">Historical!F27</f>
         <v>0.247670426679745</v>
       </c>
-      <c r="G27" s="39" t="n">
+      <c r="G27" s="37" t="n">
         <f aca="false">Historical!G27</f>
         <v>0.270011947431302</v>
       </c>
@@ -7463,113 +7445,113 @@
       <c r="A30" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="44" t="n">
+      <c r="C30" s="42" t="n">
         <f aca="false">Historical!C30</f>
         <v>153.2</v>
       </c>
-      <c r="D30" s="44" t="n">
+      <c r="D30" s="42" t="n">
         <f aca="false">Historical!D30</f>
         <v>154.4</v>
       </c>
-      <c r="E30" s="44" t="n">
+      <c r="E30" s="42" t="n">
         <f aca="false">Historical!E30</f>
         <v>192.3</v>
       </c>
-      <c r="F30" s="44" t="n">
+      <c r="F30" s="42" t="n">
         <f aca="false">Historical!F30</f>
         <v>209.4</v>
       </c>
-      <c r="G30" s="44" t="n">
+      <c r="G30" s="42" t="n">
         <f aca="false">Historical!G30</f>
         <v>183.7</v>
       </c>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="44" t="n">
+      <c r="C31" s="42" t="n">
         <f aca="false">Historical!C31</f>
         <v>145.6</v>
       </c>
-      <c r="D31" s="44" t="n">
+      <c r="D31" s="42" t="n">
         <f aca="false">Historical!D31</f>
         <v>148.3</v>
       </c>
-      <c r="E31" s="44" t="n">
+      <c r="E31" s="42" t="n">
         <f aca="false">Historical!E31</f>
         <v>188.3</v>
       </c>
-      <c r="F31" s="44" t="n">
+      <c r="F31" s="42" t="n">
         <f aca="false">Historical!F31</f>
         <v>203.9</v>
       </c>
-      <c r="G31" s="44" t="n">
+      <c r="G31" s="42" t="n">
         <f aca="false">Historical!G31</f>
         <v>167.4</v>
       </c>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="44" t="n">
+      <c r="C32" s="42" t="n">
         <f aca="false">Historical!C32</f>
         <v>117.5</v>
       </c>
-      <c r="D32" s="44" t="n">
+      <c r="D32" s="42" t="n">
         <f aca="false">Historical!D32</f>
         <v>120.3</v>
       </c>
-      <c r="E32" s="44" t="n">
+      <c r="E32" s="42" t="n">
         <f aca="false">Historical!E32</f>
         <v>142.5</v>
       </c>
-      <c r="F32" s="44" t="n">
+      <c r="F32" s="42" t="n">
         <f aca="false">Historical!F32</f>
         <v>153.4</v>
       </c>
-      <c r="G32" s="44" t="n">
+      <c r="G32" s="42" t="n">
         <f aca="false">Historical!G32</f>
         <v>122.2</v>
       </c>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="44" t="n">
+      <c r="C33" s="42" t="n">
         <f aca="false">Historical!C33</f>
         <v>145.6</v>
       </c>
-      <c r="D33" s="44" t="n">
+      <c r="D33" s="42" t="n">
         <f aca="false">Historical!D33</f>
         <v>148.3</v>
       </c>
-      <c r="E33" s="44" t="n">
+      <c r="E33" s="42" t="n">
         <f aca="false">Historical!E33</f>
         <v>167.7</v>
       </c>
-      <c r="F33" s="44" t="n">
+      <c r="F33" s="42" t="n">
         <f aca="false">Historical!F33</f>
         <v>189.8</v>
       </c>
-      <c r="G33" s="44" t="n">
+      <c r="G33" s="42" t="n">
         <f aca="false">Historical!G33</f>
         <v>171.9</v>
       </c>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
@@ -7592,23 +7574,23 @@
       <c r="B36" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="C36" s="44" t="n">
+      <c r="C36" s="42" t="n">
         <f aca="false">Historical!C36</f>
         <v>1098.2</v>
       </c>
-      <c r="D36" s="44" t="n">
+      <c r="D36" s="42" t="n">
         <f aca="false">Historical!D36</f>
         <v>1352.3</v>
       </c>
-      <c r="E36" s="44" t="n">
+      <c r="E36" s="42" t="n">
         <f aca="false">Historical!E36</f>
         <v>1610.9</v>
       </c>
-      <c r="F36" s="44" t="n">
+      <c r="F36" s="42" t="n">
         <f aca="false">Historical!F36</f>
         <v>1781.7</v>
       </c>
-      <c r="G36" s="44" t="n">
+      <c r="G36" s="42" t="n">
         <f aca="false">Historical!G36</f>
         <v>1897.2</v>
       </c>
@@ -7632,23 +7614,23 @@
       <c r="B37" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="C37" s="44" t="n">
+      <c r="C37" s="42" t="n">
         <f aca="false">Historical!C37</f>
         <v>131.5</v>
       </c>
-      <c r="D37" s="44" t="n">
+      <c r="D37" s="42" t="n">
         <f aca="false">Historical!D37</f>
         <v>160.5</v>
       </c>
-      <c r="E37" s="44" t="n">
+      <c r="E37" s="42" t="n">
         <f aca="false">Historical!E37</f>
         <v>198.7</v>
       </c>
-      <c r="F37" s="44" t="n">
+      <c r="F37" s="42" t="n">
         <f aca="false">Historical!F37</f>
         <v>232.7</v>
       </c>
-      <c r="G37" s="44" t="n">
+      <c r="G37" s="42" t="n">
         <f aca="false">Historical!G37</f>
         <v>254</v>
       </c>
@@ -7669,23 +7651,23 @@
       <c r="A38" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="44" t="n">
+      <c r="C38" s="42" t="n">
         <f aca="false">Historical!C38</f>
         <v>0</v>
       </c>
-      <c r="D38" s="44" t="n">
+      <c r="D38" s="42" t="n">
         <f aca="false">Historical!D38</f>
         <v>0</v>
       </c>
-      <c r="E38" s="44" t="n">
+      <c r="E38" s="42" t="n">
         <f aca="false">Historical!E38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="44" t="n">
+      <c r="F38" s="42" t="n">
         <f aca="false">Historical!F38</f>
         <v>0</v>
       </c>
-      <c r="G38" s="44" t="n">
+      <c r="G38" s="42" t="n">
         <f aca="false">Historical!G38</f>
         <v>0</v>
       </c>
@@ -7706,23 +7688,23 @@
       <c r="A39" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="38" t="n">
+      <c r="C39" s="36" t="n">
         <f aca="false">Historical!C39</f>
         <v>2078</v>
       </c>
-      <c r="D39" s="38" t="n">
+      <c r="D39" s="36" t="n">
         <f aca="false">Historical!D39</f>
         <v>2181</v>
       </c>
-      <c r="E39" s="38" t="n">
+      <c r="E39" s="36" t="n">
         <f aca="false">Historical!E39</f>
         <v>2328</v>
       </c>
-      <c r="F39" s="38" t="n">
+      <c r="F39" s="36" t="n">
         <f aca="false">Historical!F39</f>
         <v>2473</v>
       </c>
-      <c r="G39" s="38" t="n">
+      <c r="G39" s="36" t="n">
         <f aca="false">Historical!G39</f>
         <v>2618</v>
       </c>
@@ -7746,23 +7728,23 @@
       <c r="B40" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="C40" s="38" t="n">
+      <c r="C40" s="36" t="n">
         <f aca="false">Historical!C40</f>
         <v>2181</v>
       </c>
-      <c r="D40" s="38" t="n">
+      <c r="D40" s="36" t="n">
         <f aca="false">Historical!D40</f>
         <v>2328</v>
       </c>
-      <c r="E40" s="38" t="n">
+      <c r="E40" s="36" t="n">
         <f aca="false">Historical!E40</f>
         <v>2473</v>
       </c>
-      <c r="F40" s="38" t="n">
+      <c r="F40" s="36" t="n">
         <f aca="false">Historical!F40</f>
         <v>2618</v>
       </c>
-      <c r="G40" s="38" t="n">
+      <c r="G40" s="36" t="n">
         <f aca="false">Historical!G40</f>
         <v>2739</v>
       </c>
@@ -7783,153 +7765,153 @@
       <c r="A41" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="38" t="n">
+      <c r="C41" s="36" t="n">
         <f aca="false">Historical!C41</f>
         <v>375</v>
       </c>
-      <c r="D41" s="38" t="n">
+      <c r="D41" s="36" t="n">
         <f aca="false">Historical!D41</f>
         <v>441</v>
       </c>
-      <c r="E41" s="38" t="n">
+      <c r="E41" s="36" t="n">
         <f aca="false">Historical!E41</f>
         <v>503</v>
       </c>
-      <c r="F41" s="38" t="n">
+      <c r="F41" s="36" t="n">
         <f aca="false">Historical!F41</f>
         <v>561</v>
       </c>
-      <c r="G41" s="38" t="n">
+      <c r="G41" s="36" t="n">
         <f aca="false">Historical!G41</f>
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="H41" s="30" t="n">
         <f aca="false">G41+(1-Drivers!$C$7)*Drivers!$C$6</f>
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="I41" s="30" t="n">
         <f aca="false">H41+(1-Drivers!$D$7)*Drivers!$D$6</f>
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="J41" s="30" t="n">
         <f aca="false">I41+(1-Drivers!$E$7)*Drivers!$E$6</f>
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="38" t="n">
+      <c r="C42" s="36" t="n">
         <f aca="false">Historical!C42</f>
         <v>1806</v>
       </c>
-      <c r="D42" s="38" t="n">
+      <c r="D42" s="36" t="n">
         <f aca="false">Historical!D42</f>
         <v>1887</v>
       </c>
-      <c r="E42" s="38" t="n">
+      <c r="E42" s="36" t="n">
         <f aca="false">Historical!E42</f>
         <v>1970</v>
       </c>
-      <c r="F42" s="38" t="n">
+      <c r="F42" s="36" t="n">
         <f aca="false">Historical!F42</f>
         <v>2057</v>
       </c>
-      <c r="G42" s="38" t="n">
+      <c r="G42" s="36" t="n">
         <f aca="false">Historical!G42</f>
-        <v>2129</v>
+        <v>2137</v>
       </c>
       <c r="H42" s="30" t="n">
         <f aca="false">IF(H41="","",H40-H41)</f>
-        <v>2192</v>
+        <v>2200</v>
       </c>
       <c r="I42" s="30" t="n">
         <f aca="false">IF(I41="","",I40-I41)</f>
-        <v>2258</v>
+        <v>2266</v>
       </c>
       <c r="J42" s="30" t="n">
         <f aca="false">IF(J41="","",J40-J41)</f>
-        <v>2324</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="38" t="n">
+      <c r="C43" s="36" t="n">
         <f aca="false">Historical!C43</f>
         <v>131</v>
       </c>
-      <c r="D43" s="38" t="n">
+      <c r="D43" s="36" t="n">
         <f aca="false">Historical!D43</f>
         <v>186</v>
       </c>
-      <c r="E43" s="38" t="n">
+      <c r="E43" s="36" t="n">
         <f aca="false">Historical!E43</f>
         <v>220</v>
       </c>
-      <c r="F43" s="38" t="n">
+      <c r="F43" s="36" t="n">
         <f aca="false">Historical!F43</f>
         <v>226</v>
       </c>
-      <c r="G43" s="38" t="n">
+      <c r="G43" s="36" t="n">
         <f aca="false">Historical!G43</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
+        <v>207</v>
+      </c>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="38" t="n">
+      <c r="C44" s="36" t="n">
         <f aca="false">Historical!C44</f>
         <v>-28</v>
       </c>
-      <c r="D44" s="38" t="n">
+      <c r="D44" s="36" t="n">
         <f aca="false">Historical!D44</f>
         <v>-39</v>
       </c>
-      <c r="E44" s="38" t="n">
+      <c r="E44" s="36" t="n">
         <f aca="false">Historical!E44</f>
         <v>-75</v>
       </c>
-      <c r="F44" s="38" t="n">
+      <c r="F44" s="36" t="n">
         <f aca="false">Historical!F44</f>
         <v>-81</v>
       </c>
-      <c r="G44" s="38" t="n">
+      <c r="G44" s="36" t="n">
         <f aca="false">Historical!G44</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
+        <v>-86</v>
+      </c>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="38" t="n">
+      <c r="C45" s="36" t="n">
         <f aca="false">Historical!C45</f>
         <v>103</v>
       </c>
-      <c r="D45" s="38" t="n">
+      <c r="D45" s="36" t="n">
         <f aca="false">Historical!D45</f>
         <v>147</v>
       </c>
-      <c r="E45" s="38" t="n">
+      <c r="E45" s="36" t="n">
         <f aca="false">Historical!E45</f>
         <v>145</v>
       </c>
-      <c r="F45" s="38" t="n">
+      <c r="F45" s="36" t="n">
         <f aca="false">Historical!F45</f>
         <v>145</v>
       </c>
-      <c r="G45" s="38" t="n">
+      <c r="G45" s="36" t="n">
         <f aca="false">Historical!G45</f>
         <v>121</v>
       </c>
@@ -7950,23 +7932,23 @@
       <c r="A46" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C46" s="38" t="n">
+      <c r="C46" s="36" t="n">
         <f aca="false">Historical!C46</f>
         <v>0</v>
       </c>
-      <c r="D46" s="38" t="n">
+      <c r="D46" s="36" t="n">
         <f aca="false">Historical!D46</f>
         <v>0</v>
       </c>
-      <c r="E46" s="38" t="n">
+      <c r="E46" s="36" t="n">
         <f aca="false">Historical!E46</f>
         <v>0</v>
       </c>
-      <c r="F46" s="38" t="n">
+      <c r="F46" s="36" t="n">
         <f aca="false">Historical!F46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="38" t="n">
+      <c r="G46" s="36" t="n">
         <f aca="false">Historical!G46</f>
         <v>0</v>
       </c>
@@ -7987,23 +7969,23 @@
       <c r="A47" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="39" t="n">
+      <c r="C47" s="37" t="n">
         <f aca="false">Historical!C47</f>
         <v>0.524</v>
       </c>
-      <c r="D47" s="39" t="n">
+      <c r="D47" s="37" t="n">
         <f aca="false">Historical!D47</f>
         <v>0.178</v>
       </c>
-      <c r="E47" s="39" t="n">
+      <c r="E47" s="37" t="n">
         <f aca="false">Historical!E47</f>
         <v>0.137</v>
       </c>
-      <c r="F47" s="39" t="n">
+      <c r="F47" s="37" t="n">
         <f aca="false">Historical!F47</f>
         <v>0.055</v>
       </c>
-      <c r="G47" s="39" t="n">
+      <c r="G47" s="37" t="n">
         <f aca="false">Historical!G47</f>
         <v>0.024</v>
       </c>
@@ -8024,63 +8006,63 @@
       <c r="A48" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="39" t="n">
+      <c r="C48" s="37" t="n">
         <f aca="false">Historical!C48</f>
         <v>0</v>
       </c>
-      <c r="D48" s="39" t="n">
+      <c r="D48" s="37" t="n">
         <f aca="false">Historical!D48</f>
         <v>0</v>
       </c>
-      <c r="E48" s="39" t="n">
+      <c r="E48" s="37" t="n">
         <f aca="false">Historical!E48</f>
         <v>0.149</v>
       </c>
-      <c r="F48" s="39" t="n">
+      <c r="F48" s="37" t="n">
         <f aca="false">Historical!F48</f>
         <v>0.074</v>
       </c>
-      <c r="G48" s="39" t="n">
+      <c r="G48" s="37" t="n">
         <f aca="false">Historical!G48</f>
         <v>0.043</v>
       </c>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="41" t="n">
+      <c r="C49" s="39" t="n">
         <f aca="false">Historical!C49</f>
         <v>0.608084163898117</v>
       </c>
-      <c r="D49" s="41" t="n">
+      <c r="D49" s="39" t="n">
         <f aca="false">Historical!D49</f>
         <v>0.732358516111562</v>
       </c>
-      <c r="E49" s="41" t="n">
+      <c r="E49" s="39" t="n">
         <f aca="false">Historical!E49</f>
         <v>0.835312418978481</v>
       </c>
-      <c r="F49" s="41" t="n">
+      <c r="F49" s="39" t="n">
         <f aca="false">Historical!F49</f>
         <v>0.884877079711944</v>
       </c>
-      <c r="G49" s="41" t="n">
+      <c r="G49" s="39" t="n">
         <f aca="false">Historical!G49</f>
-        <v>0.906450071667463</v>
-      </c>
-      <c r="H49" s="35" t="n">
+        <v>0.904721030042919</v>
+      </c>
+      <c r="H49" s="33" t="n">
         <f aca="false">IF(H42="","",H36/AVERAGE(H42,IF(G42="",H42,G42)))</f>
         <v>0</v>
       </c>
-      <c r="I49" s="35" t="n">
+      <c r="I49" s="33" t="n">
         <f aca="false">IF(I42="","",I36/AVERAGE(I42,IF(H42="",I42,H42)))</f>
         <v>0</v>
       </c>
-      <c r="J49" s="35" t="n">
+      <c r="J49" s="33" t="n">
         <f aca="false">IF(J42="","",J36/AVERAGE(J42,IF(I42="",J42,I42)))</f>
         <v>0</v>
       </c>
@@ -8103,23 +8085,23 @@
       <c r="A52" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C52" s="44" t="n">
+      <c r="C52" s="42" t="n">
         <f aca="false">Historical!C52</f>
         <v>14.9</v>
       </c>
-      <c r="D52" s="44" t="n">
+      <c r="D52" s="42" t="n">
         <f aca="false">Historical!D52</f>
         <v>13.5</v>
       </c>
-      <c r="E52" s="44" t="n">
+      <c r="E52" s="42" t="n">
         <f aca="false">Historical!E52</f>
         <v>18.3</v>
       </c>
-      <c r="F52" s="44" t="n">
+      <c r="F52" s="42" t="n">
         <f aca="false">Historical!F52</f>
         <v>24.9</v>
       </c>
-      <c r="G52" s="44" t="n">
+      <c r="G52" s="42" t="n">
         <f aca="false">Historical!G52</f>
         <v>43</v>
       </c>
@@ -8143,23 +8125,23 @@
       <c r="B53" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C53" s="44" t="n">
+      <c r="C53" s="42" t="n">
         <f aca="false">Historical!C53</f>
         <v>343.8</v>
       </c>
-      <c r="D53" s="44" t="n">
+      <c r="D53" s="42" t="n">
         <f aca="false">Historical!D53</f>
         <v>390</v>
       </c>
-      <c r="E53" s="44" t="n">
+      <c r="E53" s="42" t="n">
         <f aca="false">Historical!E53</f>
         <v>510.3</v>
       </c>
-      <c r="F53" s="44" t="n">
+      <c r="F53" s="42" t="n">
         <f aca="false">Historical!F53</f>
         <v>664.7</v>
       </c>
-      <c r="G53" s="44" t="n">
+      <c r="G53" s="42" t="n">
         <f aca="false">Historical!G53</f>
         <v>832.1</v>
       </c>
@@ -8183,60 +8165,60 @@
       <c r="B54" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="C54" s="44" t="n">
+      <c r="C54" s="42" t="n">
         <f aca="false">Historical!C54</f>
         <v>263.6</v>
       </c>
-      <c r="D54" s="44" t="n">
+      <c r="D54" s="42" t="n">
         <f aca="false">Historical!D54</f>
         <v>281.6</v>
       </c>
-      <c r="E54" s="44" t="n">
+      <c r="E54" s="42" t="n">
         <f aca="false">Historical!E54</f>
         <v>296.6</v>
       </c>
-      <c r="F54" s="44" t="n">
+      <c r="F54" s="42" t="n">
         <f aca="false">Historical!F54</f>
         <v>387.2</v>
       </c>
-      <c r="G54" s="44" t="n">
+      <c r="G54" s="42" t="n">
         <f aca="false">Historical!G54</f>
         <v>413</v>
       </c>
       <c r="H54" s="28" t="n">
         <f aca="false">G54*H42/G42</f>
-        <v>425.221230624706</v>
+        <v>425.175479644361</v>
       </c>
       <c r="I54" s="28" t="n">
         <f aca="false">H54*I42/H42</f>
-        <v>438.024424612494</v>
+        <v>437.930744033692</v>
       </c>
       <c r="J54" s="28" t="n">
         <f aca="false">I54*J42/I42</f>
-        <v>450.827618600282</v>
+        <v>450.686008423023</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="44" t="n">
+      <c r="C55" s="42" t="n">
         <f aca="false">Historical!C55</f>
         <v>0</v>
       </c>
-      <c r="D55" s="44" t="n">
+      <c r="D55" s="42" t="n">
         <f aca="false">Historical!D55</f>
         <v>6.3</v>
       </c>
-      <c r="E55" s="44" t="n">
+      <c r="E55" s="42" t="n">
         <f aca="false">Historical!E55</f>
         <v>6.6</v>
       </c>
-      <c r="F55" s="44" t="n">
+      <c r="F55" s="42" t="n">
         <f aca="false">Historical!F55</f>
         <v>0</v>
       </c>
-      <c r="G55" s="44" t="n">
+      <c r="G55" s="42" t="n">
         <f aca="false">Historical!G55</f>
         <v>0</v>
       </c>
@@ -8257,37 +8239,37 @@
       <c r="A56" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="44" t="n">
+      <c r="C56" s="42" t="n">
         <f aca="false">Historical!C56</f>
         <v>622.3</v>
       </c>
-      <c r="D56" s="44" t="n">
+      <c r="D56" s="42" t="n">
         <f aca="false">Historical!D56</f>
         <v>691.4</v>
       </c>
-      <c r="E56" s="44" t="n">
+      <c r="E56" s="42" t="n">
         <f aca="false">Historical!E56</f>
         <v>831.8</v>
       </c>
-      <c r="F56" s="44" t="n">
+      <c r="F56" s="42" t="n">
         <f aca="false">Historical!F56</f>
         <v>1076.8</v>
       </c>
-      <c r="G56" s="44" t="n">
+      <c r="G56" s="42" t="n">
         <f aca="false">Historical!G56</f>
         <v>1288.1</v>
       </c>
-      <c r="H56" s="46" t="n">
+      <c r="H56" s="44" t="n">
         <f aca="false">SUM(H52:H55)</f>
-        <v>1360.24773062471</v>
-      </c>
-      <c r="I56" s="46" t="n">
+        <v>1360.20197964436</v>
+      </c>
+      <c r="I56" s="44" t="n">
         <f aca="false">SUM(I52:I55)</f>
-        <v>1409.58764711249</v>
-      </c>
-      <c r="J56" s="46" t="n">
+        <v>1409.49396653369</v>
+      </c>
+      <c r="J56" s="44" t="n">
         <f aca="false">SUM(J52:J55)</f>
-        <v>1448.80335206278</v>
+        <v>1448.66174188552</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8297,23 +8279,23 @@
       <c r="B57" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="C57" s="44" t="n">
+      <c r="C57" s="42" t="n">
         <f aca="false">Historical!C57</f>
         <v>27.9</v>
       </c>
-      <c r="D57" s="44" t="n">
+      <c r="D57" s="42" t="n">
         <f aca="false">Historical!D57</f>
         <v>40.6</v>
       </c>
-      <c r="E57" s="44" t="n">
+      <c r="E57" s="42" t="n">
         <f aca="false">Historical!E57</f>
         <v>48.8</v>
       </c>
-      <c r="F57" s="44" t="n">
+      <c r="F57" s="42" t="n">
         <f aca="false">Historical!F57</f>
         <v>55.2</v>
       </c>
-      <c r="G57" s="44" t="n">
+      <c r="G57" s="42" t="n">
         <f aca="false">Historical!G57</f>
         <v>55.7</v>
       </c>
@@ -8337,23 +8319,23 @@
       <c r="B58" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="C58" s="44" t="n">
+      <c r="C58" s="42" t="n">
         <f aca="false">Historical!C58</f>
         <v>37.6</v>
       </c>
-      <c r="D58" s="44" t="n">
+      <c r="D58" s="42" t="n">
         <f aca="false">Historical!D58</f>
         <v>50.2</v>
       </c>
-      <c r="E58" s="44" t="n">
+      <c r="E58" s="42" t="n">
         <f aca="false">Historical!E58</f>
         <v>53.8</v>
       </c>
-      <c r="F58" s="44" t="n">
+      <c r="F58" s="42" t="n">
         <f aca="false">Historical!F58</f>
         <v>62.4</v>
       </c>
-      <c r="G58" s="44" t="n">
+      <c r="G58" s="42" t="n">
         <f aca="false">Historical!G58</f>
         <v>69.4</v>
       </c>
@@ -8374,23 +8356,23 @@
       <c r="A59" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="44" t="n">
+      <c r="C59" s="42" t="n">
         <f aca="false">Historical!C59</f>
         <v>1.6</v>
       </c>
-      <c r="D59" s="44" t="n">
+      <c r="D59" s="42" t="n">
         <f aca="false">Historical!D59</f>
         <v>0</v>
       </c>
-      <c r="E59" s="44" t="n">
+      <c r="E59" s="42" t="n">
         <f aca="false">Historical!E59</f>
         <v>0</v>
       </c>
-      <c r="F59" s="44" t="n">
+      <c r="F59" s="42" t="n">
         <f aca="false">Historical!F59</f>
         <v>0</v>
       </c>
-      <c r="G59" s="44" t="n">
+      <c r="G59" s="42" t="n">
         <f aca="false">Historical!G59</f>
         <v>0</v>
       </c>
@@ -8411,23 +8393,23 @@
       <c r="A60" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="C60" s="44" t="n">
+      <c r="C60" s="42" t="n">
         <f aca="false">Historical!C60</f>
         <v>0.4</v>
       </c>
-      <c r="D60" s="44" t="n">
+      <c r="D60" s="42" t="n">
         <f aca="false">Historical!D60</f>
         <v>0.6</v>
       </c>
-      <c r="E60" s="44" t="n">
+      <c r="E60" s="42" t="n">
         <f aca="false">Historical!E60</f>
         <v>0</v>
       </c>
-      <c r="F60" s="44" t="n">
+      <c r="F60" s="42" t="n">
         <f aca="false">Historical!F60</f>
         <v>0</v>
       </c>
-      <c r="G60" s="44" t="n">
+      <c r="G60" s="42" t="n">
         <f aca="false">Historical!G60</f>
         <v>0</v>
       </c>
@@ -8451,111 +8433,111 @@
       <c r="B61" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C61" s="44" t="n">
+      <c r="C61" s="42" t="n">
         <f aca="false">Historical!C61</f>
         <v>198.6</v>
       </c>
-      <c r="D61" s="44" t="n">
+      <c r="D61" s="42" t="n">
         <f aca="false">Historical!D61</f>
         <v>191.6</v>
       </c>
-      <c r="E61" s="44" t="n">
+      <c r="E61" s="42" t="n">
         <f aca="false">Historical!E61</f>
         <v>195.3</v>
       </c>
-      <c r="F61" s="44" t="n">
+      <c r="F61" s="42" t="n">
         <f aca="false">Historical!F61</f>
         <v>125.3</v>
       </c>
-      <c r="G61" s="44" t="n">
+      <c r="G61" s="42" t="n">
         <f aca="false">Historical!G61</f>
         <v>70.8</v>
       </c>
       <c r="H61" s="28" t="n">
         <f aca="false">H113</f>
-        <v>-210.091091046031</v>
+        <v>-210.095167646701</v>
       </c>
       <c r="I61" s="28" t="n">
         <f aca="false">I113</f>
-        <v>-359.875536943741</v>
+        <v>-359.882446244934</v>
       </c>
       <c r="J61" s="28" t="n">
         <f aca="false">J113</f>
-        <v>-483.786203138412</v>
+        <v>-483.794438638808</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C62" s="44" t="n">
+      <c r="C62" s="42" t="n">
         <f aca="false">Historical!C62</f>
         <v>266.1</v>
       </c>
-      <c r="D62" s="44" t="n">
+      <c r="D62" s="42" t="n">
         <f aca="false">Historical!D62</f>
         <v>283</v>
       </c>
-      <c r="E62" s="44" t="n">
+      <c r="E62" s="42" t="n">
         <f aca="false">Historical!E62</f>
         <v>297.9</v>
       </c>
-      <c r="F62" s="44" t="n">
+      <c r="F62" s="42" t="n">
         <f aca="false">Historical!F62</f>
         <v>242.9</v>
       </c>
-      <c r="G62" s="44" t="n">
+      <c r="G62" s="42" t="n">
         <f aca="false">Historical!G62</f>
         <v>195.9</v>
       </c>
-      <c r="H62" s="46" t="n">
+      <c r="H62" s="44" t="n">
         <f aca="false">SUM(H57:H61)</f>
-        <v>-210.091091046031</v>
-      </c>
-      <c r="I62" s="46" t="n">
+        <v>-210.095167646701</v>
+      </c>
+      <c r="I62" s="44" t="n">
         <f aca="false">SUM(I57:I61)</f>
-        <v>-359.875536943741</v>
-      </c>
-      <c r="J62" s="46" t="n">
+        <v>-359.882446244934</v>
+      </c>
+      <c r="J62" s="44" t="n">
         <f aca="false">SUM(J57:J61)</f>
-        <v>-483.786203138412</v>
+        <v>-483.794438638808</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C63" s="44" t="n">
+      <c r="C63" s="42" t="n">
         <f aca="false">Historical!C63</f>
         <v>888.4</v>
       </c>
-      <c r="D63" s="44" t="n">
+      <c r="D63" s="42" t="n">
         <f aca="false">Historical!D63</f>
         <v>974.4</v>
       </c>
-      <c r="E63" s="44" t="n">
+      <c r="E63" s="42" t="n">
         <f aca="false">Historical!E63</f>
         <v>1129.7</v>
       </c>
-      <c r="F63" s="44" t="n">
+      <c r="F63" s="42" t="n">
         <f aca="false">Historical!F63</f>
         <v>1319.7</v>
       </c>
-      <c r="G63" s="44" t="n">
+      <c r="G63" s="42" t="n">
         <f aca="false">Historical!G63</f>
         <v>1484</v>
       </c>
-      <c r="H63" s="46" t="n">
+      <c r="H63" s="44" t="n">
         <f aca="false">H56+H62</f>
-        <v>1150.15663957868</v>
-      </c>
-      <c r="I63" s="46" t="n">
+        <v>1150.10681199766</v>
+      </c>
+      <c r="I63" s="44" t="n">
         <f aca="false">I56+I62</f>
-        <v>1049.71211016875</v>
-      </c>
-      <c r="J63" s="46" t="n">
+        <v>1049.61152028876</v>
+      </c>
+      <c r="J63" s="44" t="n">
         <f aca="false">J56+J62</f>
-        <v>965.01714892437</v>
+        <v>964.867303246715</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8565,23 +8547,23 @@
       <c r="B64" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="C64" s="44" t="n">
+      <c r="C64" s="42" t="n">
         <f aca="false">Historical!C64</f>
         <v>-153.4</v>
       </c>
-      <c r="D64" s="44" t="n">
+      <c r="D64" s="42" t="n">
         <f aca="false">Historical!D64</f>
         <v>-191.7</v>
       </c>
-      <c r="E64" s="44" t="n">
+      <c r="E64" s="42" t="n">
         <f aca="false">Historical!E64</f>
         <v>-211.1</v>
       </c>
-      <c r="F64" s="44" t="n">
+      <c r="F64" s="42" t="n">
         <f aca="false">Historical!F64</f>
         <v>-243.9</v>
       </c>
-      <c r="G64" s="44" t="n">
+      <c r="G64" s="42" t="n">
         <f aca="false">Historical!G64</f>
         <v>-272.8</v>
       </c>
@@ -8602,23 +8584,23 @@
       <c r="A65" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="44" t="n">
+      <c r="C65" s="42" t="n">
         <f aca="false">Historical!C65</f>
         <v>0</v>
       </c>
-      <c r="D65" s="44" t="n">
+      <c r="D65" s="42" t="n">
         <f aca="false">Historical!D65</f>
         <v>0</v>
       </c>
-      <c r="E65" s="44" t="n">
+      <c r="E65" s="42" t="n">
         <f aca="false">Historical!E65</f>
         <v>-4.9</v>
       </c>
-      <c r="F65" s="44" t="n">
+      <c r="F65" s="42" t="n">
         <f aca="false">Historical!F65</f>
         <v>-9.1</v>
       </c>
-      <c r="G65" s="44" t="n">
+      <c r="G65" s="42" t="n">
         <f aca="false">Historical!G65</f>
         <v>-2.1</v>
       </c>
@@ -8642,60 +8624,60 @@
       <c r="B66" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C66" s="44" t="n">
+      <c r="C66" s="42" t="n">
         <f aca="false">Historical!C66</f>
         <v>-49.3</v>
       </c>
-      <c r="D66" s="44" t="n">
+      <c r="D66" s="42" t="n">
         <f aca="false">Historical!D66</f>
         <v>-48.8</v>
       </c>
-      <c r="E66" s="44" t="n">
+      <c r="E66" s="42" t="n">
         <f aca="false">Historical!E66</f>
         <v>-52.5</v>
       </c>
-      <c r="F66" s="44" t="n">
+      <c r="F66" s="42" t="n">
         <f aca="false">Historical!F66</f>
         <v>-53.8</v>
       </c>
-      <c r="G66" s="44" t="n">
+      <c r="G66" s="42" t="n">
         <f aca="false">Historical!G66</f>
         <v>-62.5</v>
       </c>
       <c r="H66" s="28" t="n">
         <f aca="false">-H146*Drivers!$C$35</f>
-        <v>-64.3723167684359</v>
+        <v>-64.3653907346748</v>
       </c>
       <c r="I66" s="28" t="n">
         <f aca="false">-I146*Drivers!$D$35</f>
-        <v>-66.3105343353687</v>
+        <v>-66.296352456715</v>
       </c>
       <c r="J66" s="28" t="n">
         <f aca="false">-J146*Drivers!$E$35</f>
-        <v>-68.2487519023016</v>
+        <v>-68.2273141787553</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C67" s="44" t="n">
+      <c r="C67" s="42" t="n">
         <f aca="false">Historical!C67</f>
         <v>-4.2</v>
       </c>
-      <c r="D67" s="44" t="n">
+      <c r="D67" s="42" t="n">
         <f aca="false">Historical!D67</f>
         <v>-3.6</v>
       </c>
-      <c r="E67" s="44" t="n">
+      <c r="E67" s="42" t="n">
         <f aca="false">Historical!E67</f>
         <v>-4</v>
       </c>
-      <c r="F67" s="44" t="n">
+      <c r="F67" s="42" t="n">
         <f aca="false">Historical!F67</f>
         <v>-3.4</v>
       </c>
-      <c r="G67" s="44" t="n">
+      <c r="G67" s="42" t="n">
         <f aca="false">Historical!G67</f>
         <v>-10.3</v>
       </c>
@@ -8716,60 +8698,60 @@
       <c r="A68" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C68" s="44" t="n">
+      <c r="C68" s="42" t="n">
         <f aca="false">Historical!C68</f>
         <v>-206.9</v>
       </c>
-      <c r="D68" s="44" t="n">
+      <c r="D68" s="42" t="n">
         <f aca="false">Historical!D68</f>
         <v>-244.1</v>
       </c>
-      <c r="E68" s="44" t="n">
+      <c r="E68" s="42" t="n">
         <f aca="false">Historical!E68</f>
         <v>-272.5</v>
       </c>
-      <c r="F68" s="44" t="n">
+      <c r="F68" s="42" t="n">
         <f aca="false">Historical!F68</f>
         <v>-310.2</v>
       </c>
-      <c r="G68" s="44" t="n">
+      <c r="G68" s="42" t="n">
         <f aca="false">Historical!G68</f>
         <v>-347.7</v>
       </c>
-      <c r="H68" s="46" t="n">
+      <c r="H68" s="44" t="n">
         <f aca="false">SUM(H64:H67)</f>
-        <v>-111.772316768436</v>
-      </c>
-      <c r="I68" s="46" t="n">
+        <v>-111.765390734675</v>
+      </c>
+      <c r="I68" s="44" t="n">
         <f aca="false">SUM(I64:I67)</f>
-        <v>-88.7105343353687</v>
-      </c>
-      <c r="J68" s="46" t="n">
+        <v>-88.696352456715</v>
+      </c>
+      <c r="J68" s="44" t="n">
         <f aca="false">SUM(J64:J67)</f>
-        <v>-80.6487519023015</v>
+        <v>-80.6273141787553</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="44" t="n">
+      <c r="C69" s="42" t="n">
         <f aca="false">Historical!C69</f>
         <v>0</v>
       </c>
-      <c r="D69" s="44" t="n">
+      <c r="D69" s="42" t="n">
         <f aca="false">Historical!D69</f>
         <v>0</v>
       </c>
-      <c r="E69" s="44" t="n">
+      <c r="E69" s="42" t="n">
         <f aca="false">Historical!E69</f>
         <v>0</v>
       </c>
-      <c r="F69" s="44" t="n">
+      <c r="F69" s="42" t="n">
         <f aca="false">Historical!F69</f>
         <v>0</v>
       </c>
-      <c r="G69" s="44" t="n">
+      <c r="G69" s="42" t="n">
         <f aca="false">Historical!G69</f>
         <v>-25</v>
       </c>
@@ -8790,23 +8772,23 @@
       <c r="A70" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C70" s="44" t="n">
+      <c r="C70" s="42" t="n">
         <f aca="false">Historical!C70</f>
         <v>-3.2</v>
       </c>
-      <c r="D70" s="44" t="n">
+      <c r="D70" s="42" t="n">
         <f aca="false">Historical!D70</f>
         <v>-2.8</v>
       </c>
-      <c r="E70" s="44" t="n">
+      <c r="E70" s="42" t="n">
         <f aca="false">Historical!E70</f>
         <v>-2.3</v>
       </c>
-      <c r="F70" s="44" t="n">
+      <c r="F70" s="42" t="n">
         <f aca="false">Historical!F70</f>
         <v>-1.8</v>
       </c>
-      <c r="G70" s="44" t="n">
+      <c r="G70" s="42" t="n">
         <f aca="false">Historical!G70</f>
         <v>-1.4</v>
       </c>
@@ -8830,60 +8812,60 @@
       <c r="B71" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C71" s="44" t="n">
+      <c r="C71" s="42" t="n">
         <f aca="false">Historical!C71</f>
         <v>-233.9</v>
       </c>
-      <c r="D71" s="44" t="n">
+      <c r="D71" s="42" t="n">
         <f aca="false">Historical!D71</f>
         <v>-252.5</v>
       </c>
-      <c r="E71" s="44" t="n">
+      <c r="E71" s="42" t="n">
         <f aca="false">Historical!E71</f>
         <v>-267.1</v>
       </c>
-      <c r="F71" s="44" t="n">
+      <c r="F71" s="42" t="n">
         <f aca="false">Historical!F71</f>
         <v>-361.3</v>
       </c>
-      <c r="G71" s="44" t="n">
+      <c r="G71" s="42" t="n">
         <f aca="false">Historical!G71</f>
         <v>-387.3</v>
       </c>
       <c r="H71" s="28" t="n">
         <f aca="false">-H146*(1-Drivers!$C$35)</f>
-        <v>-398.73787581024</v>
+        <v>-398.694974262985</v>
       </c>
       <c r="I71" s="28" t="n">
         <f aca="false">-I146*(1-Drivers!$D$35)</f>
-        <v>-410.743669516205</v>
+        <v>-410.655823490875</v>
       </c>
       <c r="J71" s="28" t="n">
         <f aca="false">-J146*(1-Drivers!$E$35)</f>
-        <v>-422.74946322217</v>
+        <v>-422.616672718765</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C72" s="44" t="n">
+      <c r="C72" s="42" t="n">
         <f aca="false">Historical!C72</f>
         <v>-10</v>
       </c>
-      <c r="D72" s="44" t="n">
+      <c r="D72" s="42" t="n">
         <f aca="false">Historical!D72</f>
         <v>-26.3</v>
       </c>
-      <c r="E72" s="44" t="n">
+      <c r="E72" s="42" t="n">
         <f aca="false">Historical!E72</f>
         <v>-54.7</v>
       </c>
-      <c r="F72" s="44" t="n">
+      <c r="F72" s="42" t="n">
         <f aca="false">Historical!F72</f>
         <v>-72.6</v>
       </c>
-      <c r="G72" s="44" t="n">
+      <c r="G72" s="42" t="n">
         <f aca="false">Historical!G72</f>
         <v>-93.7</v>
       </c>
@@ -8904,23 +8886,23 @@
       <c r="A73" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="44" t="n">
+      <c r="C73" s="42" t="n">
         <f aca="false">Historical!C73</f>
         <v>-2.8</v>
       </c>
-      <c r="D73" s="44" t="n">
+      <c r="D73" s="42" t="n">
         <f aca="false">Historical!D73</f>
         <v>-2.7</v>
       </c>
-      <c r="E73" s="44" t="n">
+      <c r="E73" s="42" t="n">
         <f aca="false">Historical!E73</f>
         <v>-2.2</v>
       </c>
-      <c r="F73" s="44" t="n">
+      <c r="F73" s="42" t="n">
         <f aca="false">Historical!F73</f>
         <v>-2.9</v>
       </c>
-      <c r="G73" s="44" t="n">
+      <c r="G73" s="42" t="n">
         <f aca="false">Historical!G73</f>
         <v>-3.4</v>
       </c>
@@ -8941,23 +8923,23 @@
       <c r="A74" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="C74" s="44" t="n">
+      <c r="C74" s="42" t="n">
         <f aca="false">Historical!C74</f>
         <v>-2.4</v>
       </c>
-      <c r="D74" s="44" t="n">
+      <c r="D74" s="42" t="n">
         <f aca="false">Historical!D74</f>
         <v>0</v>
       </c>
-      <c r="E74" s="44" t="n">
+      <c r="E74" s="42" t="n">
         <f aca="false">Historical!E74</f>
         <v>0</v>
       </c>
-      <c r="F74" s="44" t="n">
+      <c r="F74" s="42" t="n">
         <f aca="false">Historical!F74</f>
         <v>-0.4</v>
       </c>
-      <c r="G74" s="44" t="n">
+      <c r="G74" s="42" t="n">
         <f aca="false">Historical!G74</f>
         <v>-0.3</v>
       </c>
@@ -8978,134 +8960,134 @@
       <c r="A75" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="44" t="n">
+      <c r="C75" s="42" t="n">
         <f aca="false">Historical!C75</f>
         <v>-252.3</v>
       </c>
-      <c r="D75" s="44" t="n">
+      <c r="D75" s="42" t="n">
         <f aca="false">Historical!D75</f>
         <v>-284.3</v>
       </c>
-      <c r="E75" s="44" t="n">
+      <c r="E75" s="42" t="n">
         <f aca="false">Historical!E75</f>
         <v>-326.3</v>
       </c>
-      <c r="F75" s="44" t="n">
+      <c r="F75" s="42" t="n">
         <f aca="false">Historical!F75</f>
         <v>-439</v>
       </c>
-      <c r="G75" s="44" t="n">
+      <c r="G75" s="42" t="n">
         <f aca="false">Historical!G75</f>
         <v>-511.1</v>
       </c>
-      <c r="H75" s="46" t="n">
+      <c r="H75" s="44" t="n">
         <f aca="false">SUM(H69:H74)</f>
-        <v>-529.12979081024</v>
-      </c>
-      <c r="I75" s="46" t="n">
+        <v>-529.086889262985</v>
+      </c>
+      <c r="I75" s="44" t="n">
         <f aca="false">SUM(I69:I74)</f>
-        <v>-545.154623991205</v>
-      </c>
-      <c r="J75" s="46" t="n">
+        <v>-545.066777965875</v>
+      </c>
+      <c r="J75" s="44" t="n">
         <f aca="false">SUM(J69:J74)</f>
-        <v>-560.065793903045</v>
+        <v>-559.93300339964</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="C76" s="44" t="n">
+      <c r="C76" s="42" t="n">
         <f aca="false">Historical!C76</f>
         <v>-459.2</v>
       </c>
-      <c r="D76" s="44" t="n">
+      <c r="D76" s="42" t="n">
         <f aca="false">Historical!D76</f>
         <v>-528.4</v>
       </c>
-      <c r="E76" s="44" t="n">
+      <c r="E76" s="42" t="n">
         <f aca="false">Historical!E76</f>
         <v>-598.8</v>
       </c>
-      <c r="F76" s="44" t="n">
+      <c r="F76" s="42" t="n">
         <f aca="false">Historical!F76</f>
         <v>-749.2</v>
       </c>
-      <c r="G76" s="44" t="n">
+      <c r="G76" s="42" t="n">
         <f aca="false">Historical!G76</f>
         <v>-858.8</v>
       </c>
-      <c r="H76" s="46" t="n">
+      <c r="H76" s="44" t="n">
         <f aca="false">H68+H75</f>
-        <v>-640.902107578675</v>
-      </c>
-      <c r="I76" s="46" t="n">
+        <v>-640.85227999766</v>
+      </c>
+      <c r="I76" s="44" t="n">
         <f aca="false">I68+I75</f>
-        <v>-633.865158326574</v>
-      </c>
-      <c r="J76" s="46" t="n">
+        <v>-633.76313042259</v>
+      </c>
+      <c r="J76" s="44" t="n">
         <f aca="false">J68+J75</f>
-        <v>-640.714545805347</v>
+        <v>-640.560317578395</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="C77" s="44" t="n">
+      <c r="C77" s="42" t="n">
         <f aca="false">Historical!C77</f>
         <v>429.2</v>
       </c>
-      <c r="D77" s="44" t="n">
+      <c r="D77" s="42" t="n">
         <f aca="false">Historical!D77</f>
         <v>446</v>
       </c>
-      <c r="E77" s="44" t="n">
+      <c r="E77" s="42" t="n">
         <f aca="false">Historical!E77</f>
         <v>530.9</v>
       </c>
-      <c r="F77" s="44" t="n">
+      <c r="F77" s="42" t="n">
         <f aca="false">Historical!F77</f>
         <v>570.5</v>
       </c>
-      <c r="G77" s="44" t="n">
+      <c r="G77" s="42" t="n">
         <f aca="false">Historical!G77</f>
         <v>625.2</v>
       </c>
-      <c r="H77" s="46" t="n">
+      <c r="H77" s="44" t="n">
         <f aca="false">H63+H76</f>
         <v>509.254532</v>
       </c>
-      <c r="I77" s="46" t="n">
+      <c r="I77" s="44" t="n">
         <f aca="false">I63+I76</f>
-        <v>415.84695184218</v>
-      </c>
-      <c r="J77" s="46" t="n">
+        <v>415.848389866168</v>
+      </c>
+      <c r="J77" s="44" t="n">
         <f aca="false">J63+J76</f>
-        <v>324.302603119023</v>
+        <v>324.30698566832</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="C78" s="44" t="n">
+      <c r="C78" s="42" t="n">
         <f aca="false">Historical!C78</f>
         <v>2</v>
       </c>
-      <c r="D78" s="44" t="n">
+      <c r="D78" s="42" t="n">
         <f aca="false">Historical!D78</f>
         <v>2</v>
       </c>
-      <c r="E78" s="44" t="n">
+      <c r="E78" s="42" t="n">
         <f aca="false">Historical!E78</f>
         <v>2</v>
       </c>
-      <c r="F78" s="44" t="n">
+      <c r="F78" s="42" t="n">
         <f aca="false">Historical!F78</f>
         <v>2</v>
       </c>
-      <c r="G78" s="44" t="n">
+      <c r="G78" s="42" t="n">
         <f aca="false">Historical!G78</f>
         <v>2</v>
       </c>
@@ -9126,23 +9108,23 @@
       <c r="A79" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C79" s="44" t="n">
+      <c r="C79" s="42" t="n">
         <f aca="false">Historical!C79</f>
         <v>20</v>
       </c>
-      <c r="D79" s="44" t="n">
+      <c r="D79" s="42" t="n">
         <f aca="false">Historical!D79</f>
         <v>23.1</v>
       </c>
-      <c r="E79" s="44" t="n">
+      <c r="E79" s="42" t="n">
         <f aca="false">Historical!E79</f>
         <v>25.1</v>
       </c>
-      <c r="F79" s="44" t="n">
+      <c r="F79" s="42" t="n">
         <f aca="false">Historical!F79</f>
         <v>25.1</v>
       </c>
-      <c r="G79" s="44" t="n">
+      <c r="G79" s="42" t="n">
         <f aca="false">Historical!G79</f>
         <v>25.1</v>
       </c>
@@ -9163,23 +9145,23 @@
       <c r="A80" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="C80" s="44" t="n">
+      <c r="C80" s="42" t="n">
         <f aca="false">Historical!C80</f>
         <v>0.4</v>
       </c>
-      <c r="D80" s="44" t="n">
+      <c r="D80" s="42" t="n">
         <f aca="false">Historical!D80</f>
         <v>0.4</v>
       </c>
-      <c r="E80" s="44" t="n">
+      <c r="E80" s="42" t="n">
         <f aca="false">Historical!E80</f>
         <v>0.4</v>
       </c>
-      <c r="F80" s="44" t="n">
+      <c r="F80" s="42" t="n">
         <f aca="false">Historical!F80</f>
         <v>0.4</v>
       </c>
-      <c r="G80" s="44" t="n">
+      <c r="G80" s="42" t="n">
         <f aca="false">Historical!G80</f>
         <v>0.4</v>
       </c>
@@ -9203,23 +9185,23 @@
       <c r="B81" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="C81" s="44" t="n">
+      <c r="C81" s="42" t="n">
         <f aca="false">Historical!C81</f>
         <v>406.8</v>
       </c>
-      <c r="D81" s="44" t="n">
+      <c r="D81" s="42" t="n">
         <f aca="false">Historical!D81</f>
         <v>420.5</v>
       </c>
-      <c r="E81" s="44" t="n">
+      <c r="E81" s="42" t="n">
         <f aca="false">Historical!E81</f>
         <v>503.4</v>
       </c>
-      <c r="F81" s="44" t="n">
+      <c r="F81" s="42" t="n">
         <f aca="false">Historical!F81</f>
         <v>543</v>
       </c>
-      <c r="G81" s="44" t="n">
+      <c r="G81" s="42" t="n">
         <f aca="false">Historical!G81</f>
         <v>597.7</v>
       </c>
@@ -9229,105 +9211,105 @@
       </c>
       <c r="I81" s="28" t="n">
         <f aca="false">H81+I18+I108</f>
-        <v>388.34695184218</v>
+        <v>388.348389866168</v>
       </c>
       <c r="J81" s="28" t="n">
         <f aca="false">I81+J18+J108</f>
-        <v>296.802603119023</v>
+        <v>296.80698566832</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="C82" s="44" t="n">
+      <c r="C82" s="42" t="n">
         <f aca="false">Historical!C82</f>
         <v>429.2</v>
       </c>
-      <c r="D82" s="44" t="n">
+      <c r="D82" s="42" t="n">
         <f aca="false">Historical!D82</f>
         <v>446</v>
       </c>
-      <c r="E82" s="44" t="n">
+      <c r="E82" s="42" t="n">
         <f aca="false">Historical!E82</f>
         <v>530.9</v>
       </c>
-      <c r="F82" s="44" t="n">
+      <c r="F82" s="42" t="n">
         <f aca="false">Historical!F82</f>
         <v>570.5</v>
       </c>
-      <c r="G82" s="44" t="n">
+      <c r="G82" s="42" t="n">
         <f aca="false">Historical!G82</f>
         <v>625.2</v>
       </c>
-      <c r="H82" s="46" t="n">
+      <c r="H82" s="44" t="n">
         <f aca="false">SUM(H78:H81)</f>
         <v>509.254532</v>
       </c>
-      <c r="I82" s="46" t="n">
+      <c r="I82" s="44" t="n">
         <f aca="false">SUM(I78:I81)</f>
-        <v>415.84695184218</v>
-      </c>
-      <c r="J82" s="46" t="n">
+        <v>415.848389866168</v>
+      </c>
+      <c r="J82" s="44" t="n">
         <f aca="false">SUM(J78:J81)</f>
-        <v>324.302603119023</v>
+        <v>324.30698566832</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="C83" s="44" t="n">
+      <c r="C83" s="42" t="n">
         <f aca="false">Historical!C83</f>
         <v>888.4</v>
       </c>
-      <c r="D83" s="44" t="n">
+      <c r="D83" s="42" t="n">
         <f aca="false">Historical!D83</f>
         <v>974.4</v>
       </c>
-      <c r="E83" s="44" t="n">
+      <c r="E83" s="42" t="n">
         <f aca="false">Historical!E83</f>
         <v>1129.7</v>
       </c>
-      <c r="F83" s="44" t="n">
+      <c r="F83" s="42" t="n">
         <f aca="false">Historical!F83</f>
         <v>1319.7</v>
       </c>
-      <c r="G83" s="44" t="n">
+      <c r="G83" s="42" t="n">
         <f aca="false">Historical!G83</f>
         <v>1484</v>
       </c>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47"/>
-      <c r="J83" s="47"/>
+      <c r="H83" s="45"/>
+      <c r="I83" s="45"/>
+      <c r="J83" s="45"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="44" t="n">
+      <c r="C84" s="42" t="n">
         <f aca="false">Historical!C84</f>
         <v>429.2</v>
       </c>
-      <c r="D84" s="44" t="n">
+      <c r="D84" s="42" t="n">
         <f aca="false">Historical!D84</f>
         <v>446</v>
       </c>
-      <c r="E84" s="44" t="n">
+      <c r="E84" s="42" t="n">
         <f aca="false">Historical!E84</f>
         <v>530.9</v>
       </c>
-      <c r="F84" s="44" t="n">
+      <c r="F84" s="42" t="n">
         <f aca="false">Historical!F84</f>
         <v>570.5</v>
       </c>
-      <c r="G84" s="44" t="n">
+      <c r="G84" s="42" t="n">
         <f aca="false">Historical!G84</f>
         <v>625.2</v>
       </c>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="47"/>
+      <c r="H84" s="45"/>
+      <c r="I84" s="45"/>
+      <c r="J84" s="45"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="21" t="s">
@@ -9347,111 +9329,111 @@
       <c r="A87" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="C87" s="44" t="n">
+      <c r="C87" s="42" t="n">
         <f aca="false">Historical!C87</f>
         <v>198.6</v>
       </c>
-      <c r="D87" s="44" t="n">
+      <c r="D87" s="42" t="n">
         <f aca="false">Historical!D87</f>
         <v>191.6</v>
       </c>
-      <c r="E87" s="44" t="n">
+      <c r="E87" s="42" t="n">
         <f aca="false">Historical!E87</f>
         <v>195.3</v>
       </c>
-      <c r="F87" s="44" t="n">
+      <c r="F87" s="42" t="n">
         <f aca="false">Historical!F87</f>
         <v>125.3</v>
       </c>
-      <c r="G87" s="44" t="n">
+      <c r="G87" s="42" t="n">
         <f aca="false">Historical!G87</f>
         <v>45.8</v>
       </c>
       <c r="H87" s="28" t="n">
         <f aca="false">H61+H69</f>
-        <v>-235.091091046031</v>
+        <v>-235.095167646701</v>
       </c>
       <c r="I87" s="28" t="n">
         <f aca="false">I61+I69</f>
-        <v>-384.875536943741</v>
+        <v>-384.882446244934</v>
       </c>
       <c r="J87" s="28" t="n">
         <f aca="false">J61+J69</f>
-        <v>-508.786203138412</v>
+        <v>-508.794438638808</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="C88" s="44" t="n">
+      <c r="C88" s="42" t="n">
         <f aca="false">Historical!C88</f>
         <v>-283.2</v>
       </c>
-      <c r="D88" s="44" t="n">
+      <c r="D88" s="42" t="n">
         <f aca="false">Historical!D88</f>
         <v>-301.3</v>
       </c>
-      <c r="E88" s="44" t="n">
+      <c r="E88" s="42" t="n">
         <f aca="false">Historical!E88</f>
         <v>-319.6</v>
       </c>
-      <c r="F88" s="44" t="n">
+      <c r="F88" s="42" t="n">
         <f aca="false">Historical!F88</f>
         <v>-415.1</v>
       </c>
-      <c r="G88" s="44" t="n">
+      <c r="G88" s="42" t="n">
         <f aca="false">Historical!G88</f>
         <v>-449.8</v>
       </c>
       <c r="H88" s="28" t="n">
         <f aca="false">H66+H71</f>
-        <v>-463.110192578675</v>
+        <v>-463.06036499766</v>
       </c>
       <c r="I88" s="28" t="n">
         <f aca="false">I66+I71</f>
-        <v>-477.054203851574</v>
+        <v>-476.95217594759</v>
       </c>
       <c r="J88" s="28" t="n">
         <f aca="false">J66+J71</f>
-        <v>-490.998215124472</v>
+        <v>-490.84398689752</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="C89" s="44" t="n">
+      <c r="C89" s="42" t="n">
         <f aca="false">Historical!C89</f>
         <v>-84.6</v>
       </c>
-      <c r="D89" s="44" t="n">
+      <c r="D89" s="42" t="n">
         <f aca="false">Historical!D89</f>
         <v>-109.7</v>
       </c>
-      <c r="E89" s="44" t="n">
+      <c r="E89" s="42" t="n">
         <f aca="false">Historical!E89</f>
         <v>-124.3</v>
       </c>
-      <c r="F89" s="44" t="n">
+      <c r="F89" s="42" t="n">
         <f aca="false">Historical!F89</f>
         <v>-289.8</v>
       </c>
-      <c r="G89" s="44" t="n">
+      <c r="G89" s="42" t="n">
         <f aca="false">Historical!G89</f>
         <v>-404</v>
       </c>
       <c r="H89" s="28" t="n">
         <f aca="false">H87+H88</f>
-        <v>-698.201283624706</v>
+        <v>-698.155532644361</v>
       </c>
       <c r="I89" s="28" t="n">
         <f aca="false">I87+I88</f>
-        <v>-861.929740795315</v>
+        <v>-861.834622192524</v>
       </c>
       <c r="J89" s="28" t="n">
         <f aca="false">J87+J88</f>
-        <v>-999.784418262884</v>
+        <v>-999.638425536328</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9472,23 +9454,23 @@
       <c r="A92" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C92" s="44" t="n">
+      <c r="C92" s="42" t="n">
         <f aca="false">Historical!C92</f>
         <v>312.1</v>
       </c>
-      <c r="D92" s="44" t="n">
+      <c r="D92" s="42" t="n">
         <f aca="false">Historical!D92</f>
         <v>272.3</v>
       </c>
-      <c r="E92" s="44" t="n">
+      <c r="E92" s="42" t="n">
         <f aca="false">Historical!E92</f>
         <v>333</v>
       </c>
-      <c r="F92" s="44" t="n">
+      <c r="F92" s="42" t="n">
         <f aca="false">Historical!F92</f>
         <v>352.6</v>
       </c>
-      <c r="G92" s="44" t="n">
+      <c r="G92" s="42" t="n">
         <f aca="false">Historical!G92</f>
         <v>383.7</v>
       </c>
@@ -9498,34 +9480,34 @@
       </c>
       <c r="I92" s="28" t="n">
         <f aca="false">I13+I145+I144+I147-(I57-H57)-(I58-H58)-(I64-H64)-(I67-H67)</f>
-        <v>165.7508867062</v>
+        <v>165.743109039541</v>
       </c>
       <c r="J92" s="28" t="n">
         <f aca="false">J13+J145+J144+J147-(J57-I57)-(J58-I58)-(J64-I64)-(J67-I67)</f>
-        <v>193.051641221624</v>
+        <v>193.035715523228</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="44" t="n">
+      <c r="C93" s="42" t="n">
         <f aca="false">Historical!C93</f>
         <v>-19.2</v>
       </c>
-      <c r="D93" s="44" t="n">
+      <c r="D93" s="42" t="n">
         <f aca="false">Historical!D93</f>
         <v>-13.3</v>
       </c>
-      <c r="E93" s="44" t="n">
+      <c r="E93" s="42" t="n">
         <f aca="false">Historical!E93</f>
         <v>-11.9</v>
       </c>
-      <c r="F93" s="44" t="n">
+      <c r="F93" s="42" t="n">
         <f aca="false">Historical!F93</f>
         <v>-27.7</v>
       </c>
-      <c r="G93" s="44" t="n">
+      <c r="G93" s="42" t="n">
         <f aca="false">Historical!G93</f>
         <v>-31.5</v>
       </c>
@@ -9535,34 +9517,34 @@
       </c>
       <c r="I93" s="28" t="n">
         <f aca="false">I17-(I72-H72)</f>
-        <v>11.6399768277478</v>
+        <v>11.6394715760763</v>
       </c>
       <c r="J93" s="28" t="n">
         <f aca="false">J17-(J72-I72)</f>
-        <v>9.36770583292996</v>
+        <v>9.36667126998357</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="C94" s="44" t="n">
+      <c r="C94" s="42" t="n">
         <f aca="false">Historical!C94</f>
         <v>0</v>
       </c>
-      <c r="D94" s="44" t="n">
+      <c r="D94" s="42" t="n">
         <f aca="false">Historical!D94</f>
         <v>1.4</v>
       </c>
-      <c r="E94" s="44" t="n">
+      <c r="E94" s="42" t="n">
         <f aca="false">Historical!E94</f>
         <v>6.1</v>
       </c>
-      <c r="F94" s="44" t="n">
+      <c r="F94" s="42" t="n">
         <f aca="false">Historical!F94</f>
         <v>7.7</v>
       </c>
-      <c r="G94" s="44" t="n">
+      <c r="G94" s="42" t="n">
         <f aca="false">Historical!G94</f>
         <v>2.1</v>
       </c>
@@ -9583,23 +9565,23 @@
       <c r="A95" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="C95" s="44" t="n">
+      <c r="C95" s="42" t="n">
         <f aca="false">Historical!C95</f>
         <v>-6.3</v>
       </c>
-      <c r="D95" s="44" t="n">
+      <c r="D95" s="42" t="n">
         <f aca="false">Historical!D95</f>
         <v>-6.8</v>
       </c>
-      <c r="E95" s="44" t="n">
+      <c r="E95" s="42" t="n">
         <f aca="false">Historical!E95</f>
         <v>-9.6</v>
       </c>
-      <c r="F95" s="44" t="n">
+      <c r="F95" s="42" t="n">
         <f aca="false">Historical!F95</f>
         <v>-13</v>
       </c>
-      <c r="G95" s="44" t="n">
+      <c r="G95" s="42" t="n">
         <f aca="false">Historical!G95</f>
         <v>-16.7</v>
       </c>
@@ -9609,34 +9591,34 @@
       </c>
       <c r="I95" s="28" t="n">
         <f aca="false">-I150</f>
-        <v>-18.0612975105683</v>
+        <v>-18.0593542349088</v>
       </c>
       <c r="J95" s="28" t="n">
         <f aca="false">-J150</f>
-        <v>-18.6051139502114</v>
+        <v>-18.601134861956</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="44" t="n">
+      <c r="C96" s="42" t="n">
         <f aca="false">Historical!C96</f>
         <v>-1.1</v>
       </c>
-      <c r="D96" s="44" t="n">
+      <c r="D96" s="42" t="n">
         <f aca="false">Historical!D96</f>
         <v>-0.7</v>
       </c>
-      <c r="E96" s="44" t="n">
+      <c r="E96" s="42" t="n">
         <f aca="false">Historical!E96</f>
         <v>-0.7</v>
       </c>
-      <c r="F96" s="44" t="n">
+      <c r="F96" s="42" t="n">
         <f aca="false">Historical!F96</f>
         <v>-1</v>
       </c>
-      <c r="G96" s="44" t="n">
+      <c r="G96" s="42" t="n">
         <f aca="false">Historical!G96</f>
         <v>-0.6</v>
       </c>
@@ -9660,60 +9642,60 @@
       <c r="B97" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C97" s="44" t="n">
+      <c r="C97" s="42" t="n">
         <f aca="false">Historical!C97</f>
         <v>285.5</v>
       </c>
-      <c r="D97" s="44" t="n">
+      <c r="D97" s="42" t="n">
         <f aca="false">Historical!D97</f>
         <v>252.9</v>
       </c>
-      <c r="E97" s="44" t="n">
+      <c r="E97" s="42" t="n">
         <f aca="false">Historical!E97</f>
         <v>316.9</v>
       </c>
-      <c r="F97" s="44" t="n">
+      <c r="F97" s="42" t="n">
         <f aca="false">Historical!F97</f>
         <v>318.6</v>
       </c>
-      <c r="G97" s="44" t="n">
+      <c r="G97" s="42" t="n">
         <f aca="false">Historical!G97</f>
         <v>337</v>
       </c>
-      <c r="H97" s="46" t="n">
+      <c r="H97" s="44" t="n">
         <f aca="false">SUM(H92:H96)</f>
         <v>38.540947</v>
       </c>
-      <c r="I97" s="46" t="n">
+      <c r="I97" s="44" t="n">
         <f aca="false">SUM(I92:I96)</f>
-        <v>158.07956602338</v>
-      </c>
-      <c r="J97" s="46" t="n">
+        <v>158.073226380709</v>
+      </c>
+      <c r="J97" s="44" t="n">
         <f aca="false">SUM(J92:J96)</f>
-        <v>182.564233104343</v>
+        <v>182.551251931255</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="44" t="n">
+      <c r="C98" s="42" t="n">
         <f aca="false">Historical!C98</f>
         <v>-50.5</v>
       </c>
-      <c r="D98" s="44" t="n">
+      <c r="D98" s="42" t="n">
         <f aca="false">Historical!D98</f>
         <v>-100</v>
       </c>
-      <c r="E98" s="44" t="n">
+      <c r="E98" s="42" t="n">
         <f aca="false">Historical!E98</f>
         <v>-189.5</v>
       </c>
-      <c r="F98" s="44" t="n">
+      <c r="F98" s="42" t="n">
         <f aca="false">Historical!F98</f>
         <v>-230</v>
       </c>
-      <c r="G98" s="44" t="n">
+      <c r="G98" s="42" t="n">
         <f aca="false">Historical!G98</f>
         <v>-263.3</v>
       </c>
@@ -9734,23 +9716,23 @@
       <c r="A99" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="44" t="n">
+      <c r="C99" s="42" t="n">
         <f aca="false">Historical!C99</f>
         <v>-3.8</v>
       </c>
-      <c r="D99" s="44" t="n">
+      <c r="D99" s="42" t="n">
         <f aca="false">Historical!D99</f>
         <v>-3.3</v>
       </c>
-      <c r="E99" s="44" t="n">
+      <c r="E99" s="42" t="n">
         <f aca="false">Historical!E99</f>
         <v>-8.6</v>
       </c>
-      <c r="F99" s="44" t="n">
+      <c r="F99" s="42" t="n">
         <f aca="false">Historical!F99</f>
         <v>-10.9</v>
       </c>
-      <c r="G99" s="44" t="n">
+      <c r="G99" s="42" t="n">
         <f aca="false">Historical!G99</f>
         <v>-22.1</v>
       </c>
@@ -9771,23 +9753,23 @@
       <c r="A100" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="C100" s="44" t="n">
+      <c r="C100" s="42" t="n">
         <f aca="false">Historical!C100</f>
         <v>0.3</v>
       </c>
-      <c r="D100" s="44" t="n">
+      <c r="D100" s="42" t="n">
         <f aca="false">Historical!D100</f>
         <v>0.9</v>
       </c>
-      <c r="E100" s="44" t="n">
+      <c r="E100" s="42" t="n">
         <f aca="false">Historical!E100</f>
         <v>0.8</v>
       </c>
-      <c r="F100" s="44" t="n">
+      <c r="F100" s="42" t="n">
         <f aca="false">Historical!F100</f>
         <v>16.1</v>
       </c>
-      <c r="G100" s="44" t="n">
+      <c r="G100" s="42" t="n">
         <f aca="false">Historical!G100</f>
         <v>0.9</v>
       </c>
@@ -9808,23 +9790,23 @@
       <c r="A101" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="C101" s="44" t="n">
+      <c r="C101" s="42" t="n">
         <f aca="false">Historical!C101</f>
         <v>0</v>
       </c>
-      <c r="D101" s="44" t="n">
+      <c r="D101" s="42" t="n">
         <f aca="false">Historical!D101</f>
         <v>1.6</v>
       </c>
-      <c r="E101" s="44" t="n">
+      <c r="E101" s="42" t="n">
         <f aca="false">Historical!E101</f>
         <v>0</v>
       </c>
-      <c r="F101" s="44" t="n">
+      <c r="F101" s="42" t="n">
         <f aca="false">Historical!F101</f>
         <v>0</v>
       </c>
-      <c r="G101" s="44" t="n">
+      <c r="G101" s="42" t="n">
         <f aca="false">Historical!G101</f>
         <v>0</v>
       </c>
@@ -9845,35 +9827,35 @@
       <c r="A102" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="C102" s="44" t="n">
+      <c r="C102" s="42" t="n">
         <f aca="false">Historical!C102</f>
         <v>-54</v>
       </c>
-      <c r="D102" s="44" t="n">
+      <c r="D102" s="42" t="n">
         <f aca="false">Historical!D102</f>
         <v>-100.8</v>
       </c>
-      <c r="E102" s="44" t="n">
+      <c r="E102" s="42" t="n">
         <f aca="false">Historical!E102</f>
         <v>-197.3</v>
       </c>
-      <c r="F102" s="44" t="n">
+      <c r="F102" s="42" t="n">
         <f aca="false">Historical!F102</f>
         <v>-224.8</v>
       </c>
-      <c r="G102" s="44" t="n">
+      <c r="G102" s="42" t="n">
         <f aca="false">Historical!G102</f>
         <v>-284.5</v>
       </c>
-      <c r="H102" s="46" t="n">
+      <c r="H102" s="44" t="n">
         <f aca="false">SUM(H98:H101)</f>
         <v>-180</v>
       </c>
-      <c r="I102" s="46" t="n">
+      <c r="I102" s="44" t="n">
         <f aca="false">SUM(I98:I101)</f>
         <v>-165</v>
       </c>
-      <c r="J102" s="46" t="n">
+      <c r="J102" s="44" t="n">
         <f aca="false">SUM(J98:J101)</f>
         <v>-160</v>
       </c>
@@ -9882,23 +9864,23 @@
       <c r="A103" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="C103" s="44" t="n">
+      <c r="C103" s="42" t="n">
         <f aca="false">Historical!C103</f>
         <v>0</v>
       </c>
-      <c r="D103" s="44" t="n">
+      <c r="D103" s="42" t="n">
         <f aca="false">Historical!D103</f>
         <v>0</v>
       </c>
-      <c r="E103" s="44" t="n">
+      <c r="E103" s="42" t="n">
         <f aca="false">Historical!E103</f>
         <v>0</v>
       </c>
-      <c r="F103" s="44" t="n">
+      <c r="F103" s="42" t="n">
         <f aca="false">Historical!F103</f>
         <v>0</v>
       </c>
-      <c r="G103" s="44" t="n">
+      <c r="G103" s="42" t="n">
         <f aca="false">Historical!G103</f>
         <v>40</v>
       </c>
@@ -9919,23 +9901,23 @@
       <c r="A104" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="C104" s="44" t="n">
+      <c r="C104" s="42" t="n">
         <f aca="false">Historical!C104</f>
         <v>0</v>
       </c>
-      <c r="D104" s="44" t="n">
+      <c r="D104" s="42" t="n">
         <f aca="false">Historical!D104</f>
         <v>0</v>
       </c>
-      <c r="E104" s="44" t="n">
+      <c r="E104" s="42" t="n">
         <f aca="false">Historical!E104</f>
         <v>0</v>
       </c>
-      <c r="F104" s="44" t="n">
+      <c r="F104" s="42" t="n">
         <f aca="false">Historical!F104</f>
         <v>0</v>
       </c>
-      <c r="G104" s="44" t="n">
+      <c r="G104" s="42" t="n">
         <f aca="false">Historical!G104</f>
         <v>-15</v>
       </c>
@@ -9956,23 +9938,23 @@
       <c r="A105" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="C105" s="44" t="n">
+      <c r="C105" s="42" t="n">
         <f aca="false">Historical!C105</f>
         <v>4.3</v>
       </c>
-      <c r="D105" s="44" t="n">
+      <c r="D105" s="42" t="n">
         <f aca="false">Historical!D105</f>
         <v>3.1</v>
       </c>
-      <c r="E105" s="44" t="n">
+      <c r="E105" s="42" t="n">
         <f aca="false">Historical!E105</f>
         <v>2</v>
       </c>
-      <c r="F105" s="44" t="n">
+      <c r="F105" s="42" t="n">
         <f aca="false">Historical!F105</f>
         <v>0</v>
       </c>
-      <c r="G105" s="44" t="n">
+      <c r="G105" s="42" t="n">
         <f aca="false">Historical!G105</f>
         <v>0</v>
       </c>
@@ -9993,23 +9975,23 @@
       <c r="A106" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="C106" s="44" t="n">
+      <c r="C106" s="42" t="n">
         <f aca="false">Historical!C106</f>
         <v>0.3</v>
       </c>
-      <c r="D106" s="44" t="n">
+      <c r="D106" s="42" t="n">
         <f aca="false">Historical!D106</f>
         <v>0</v>
       </c>
-      <c r="E106" s="44" t="n">
+      <c r="E106" s="42" t="n">
         <f aca="false">Historical!E106</f>
         <v>1.6</v>
       </c>
-      <c r="F106" s="44" t="n">
+      <c r="F106" s="42" t="n">
         <f aca="false">Historical!F106</f>
         <v>4.7</v>
       </c>
-      <c r="G106" s="44" t="n">
+      <c r="G106" s="42" t="n">
         <f aca="false">Historical!G106</f>
         <v>1.6</v>
       </c>
@@ -10030,23 +10012,23 @@
       <c r="A107" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="C107" s="44" t="n">
+      <c r="C107" s="42" t="n">
         <f aca="false">Historical!C107</f>
         <v>-10</v>
       </c>
-      <c r="D107" s="44" t="n">
+      <c r="D107" s="42" t="n">
         <f aca="false">Historical!D107</f>
         <v>-11</v>
       </c>
-      <c r="E107" s="44" t="n">
+      <c r="E107" s="42" t="n">
         <f aca="false">Historical!E107</f>
         <v>-5</v>
       </c>
-      <c r="F107" s="44" t="n">
+      <c r="F107" s="42" t="n">
         <f aca="false">Historical!F107</f>
         <v>-5</v>
       </c>
-      <c r="G107" s="44" t="n">
+      <c r="G107" s="42" t="n">
         <f aca="false">Historical!G107</f>
         <v>0</v>
       </c>
@@ -10070,23 +10052,23 @@
       <c r="B108" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="C108" s="44" t="n">
+      <c r="C108" s="42" t="n">
         <f aca="false">Historical!C108</f>
         <v>-15.3</v>
       </c>
-      <c r="D108" s="44" t="n">
+      <c r="D108" s="42" t="n">
         <f aca="false">Historical!D108</f>
         <v>-98.5</v>
       </c>
-      <c r="E108" s="44" t="n">
+      <c r="E108" s="42" t="n">
         <f aca="false">Historical!E108</f>
         <v>-60.8</v>
       </c>
-      <c r="F108" s="44" t="n">
+      <c r="F108" s="42" t="n">
         <f aca="false">Historical!F108</f>
         <v>-106.8</v>
       </c>
-      <c r="G108" s="44" t="n">
+      <c r="G108" s="42" t="n">
         <f aca="false">Historical!G108</f>
         <v>-70.3</v>
       </c>
@@ -10107,134 +10089,134 @@
       <c r="A109" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="C109" s="44" t="n">
+      <c r="C109" s="42" t="n">
         <f aca="false">Historical!C109</f>
         <v>-49</v>
       </c>
-      <c r="D109" s="44" t="n">
+      <c r="D109" s="42" t="n">
         <f aca="false">Historical!D109</f>
         <v>-52.7</v>
       </c>
-      <c r="E109" s="44" t="n">
+      <c r="E109" s="42" t="n">
         <f aca="false">Historical!E109</f>
         <v>-53.7</v>
       </c>
-      <c r="F109" s="44" t="n">
+      <c r="F109" s="42" t="n">
         <f aca="false">Historical!F109</f>
         <v>-56.7</v>
       </c>
-      <c r="G109" s="44" t="n">
+      <c r="G109" s="42" t="n">
         <f aca="false">Historical!G109</f>
         <v>-63.3</v>
       </c>
       <c r="H109" s="28" t="n">
         <f aca="false">-H149</f>
-        <v>-69.121038046031</v>
+        <v>-69.125114646701</v>
       </c>
       <c r="I109" s="28" t="n">
         <f aca="false">-I149</f>
-        <v>-71.1467919210897</v>
+        <v>-71.1432849789424</v>
       </c>
       <c r="J109" s="28" t="n">
         <f aca="false">-J149</f>
-        <v>-73.3233348990137</v>
+        <v>-73.3116799251287</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C110" s="44" t="n">
+      <c r="C110" s="42" t="n">
         <f aca="false">Historical!C110</f>
         <v>-69.7</v>
       </c>
-      <c r="D110" s="44" t="n">
+      <c r="D110" s="42" t="n">
         <f aca="false">Historical!D110</f>
         <v>-159.1</v>
       </c>
-      <c r="E110" s="44" t="n">
+      <c r="E110" s="42" t="n">
         <f aca="false">Historical!E110</f>
         <v>-115.9</v>
       </c>
-      <c r="F110" s="44" t="n">
+      <c r="F110" s="42" t="n">
         <f aca="false">Historical!F110</f>
         <v>-163.8</v>
       </c>
-      <c r="G110" s="44" t="n">
+      <c r="G110" s="42" t="n">
         <f aca="false">Historical!G110</f>
         <v>-107</v>
       </c>
-      <c r="H110" s="46" t="n">
+      <c r="H110" s="44" t="n">
         <f aca="false">SUM(H103:H109)</f>
-        <v>-139.432038046031</v>
-      </c>
-      <c r="I110" s="46" t="n">
+        <v>-139.436114646701</v>
+      </c>
+      <c r="I110" s="44" t="n">
         <f aca="false">SUM(I103:I109)</f>
-        <v>-142.86401192109</v>
-      </c>
-      <c r="J110" s="46" t="n">
+        <v>-142.860504978942</v>
+      </c>
+      <c r="J110" s="44" t="n">
         <f aca="false">SUM(J103:J109)</f>
-        <v>-146.474899299014</v>
+        <v>-146.463244325129</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="C111" s="44" t="n">
+      <c r="C111" s="42" t="n">
         <f aca="false">Historical!C111</f>
         <v>161.8</v>
       </c>
-      <c r="D111" s="44" t="n">
+      <c r="D111" s="42" t="n">
         <f aca="false">Historical!D111</f>
         <v>-6.99999999999997</v>
       </c>
-      <c r="E111" s="44" t="n">
+      <c r="E111" s="42" t="n">
         <f aca="false">Historical!E111</f>
         <v>3.69999999999996</v>
       </c>
-      <c r="F111" s="44" t="n">
+      <c r="F111" s="42" t="n">
         <f aca="false">Historical!F111</f>
         <v>-70</v>
       </c>
-      <c r="G111" s="44" t="n">
+      <c r="G111" s="42" t="n">
         <f aca="false">Historical!G111</f>
         <v>-54.5</v>
       </c>
-      <c r="H111" s="46" t="n">
+      <c r="H111" s="44" t="n">
         <f aca="false">H97+H102+H110</f>
-        <v>-280.891091046031</v>
-      </c>
-      <c r="I111" s="46" t="n">
+        <v>-280.895167646701</v>
+      </c>
+      <c r="I111" s="44" t="n">
         <f aca="false">I97+I102+I110</f>
-        <v>-149.78444589771</v>
-      </c>
-      <c r="J111" s="46" t="n">
+        <v>-149.787278598233</v>
+      </c>
+      <c r="J111" s="44" t="n">
         <f aca="false">J97+J102+J110</f>
-        <v>-123.910666194671</v>
+        <v>-123.911992393873</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C112" s="44" t="n">
+      <c r="C112" s="42" t="n">
         <f aca="false">Historical!C112</f>
         <v>36.8</v>
       </c>
-      <c r="D112" s="44" t="n">
+      <c r="D112" s="42" t="n">
         <f aca="false">Historical!D112</f>
         <v>198.6</v>
       </c>
-      <c r="E112" s="44" t="n">
+      <c r="E112" s="42" t="n">
         <f aca="false">Historical!E112</f>
         <v>191.6</v>
       </c>
-      <c r="F112" s="44" t="n">
+      <c r="F112" s="42" t="n">
         <f aca="false">Historical!F112</f>
         <v>195.3</v>
       </c>
-      <c r="G112" s="44" t="n">
+      <c r="G112" s="42" t="n">
         <f aca="false">Historical!G112</f>
         <v>125.3</v>
       </c>
@@ -10244,77 +10226,77 @@
       </c>
       <c r="I112" s="28" t="n">
         <f aca="false">H113</f>
-        <v>-210.091091046031</v>
+        <v>-210.095167646701</v>
       </c>
       <c r="J112" s="28" t="n">
         <f aca="false">I113</f>
-        <v>-359.875536943741</v>
+        <v>-359.882446244934</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C113" s="44" t="n">
+      <c r="C113" s="42" t="n">
         <f aca="false">Historical!C113</f>
         <v>198.6</v>
       </c>
-      <c r="D113" s="44" t="n">
+      <c r="D113" s="42" t="n">
         <f aca="false">Historical!D113</f>
         <v>191.6</v>
       </c>
-      <c r="E113" s="44" t="n">
+      <c r="E113" s="42" t="n">
         <f aca="false">Historical!E113</f>
         <v>195.3</v>
       </c>
-      <c r="F113" s="44" t="n">
+      <c r="F113" s="42" t="n">
         <f aca="false">Historical!F113</f>
         <v>125.3</v>
       </c>
-      <c r="G113" s="44" t="n">
+      <c r="G113" s="42" t="n">
         <f aca="false">Historical!G113</f>
         <v>70.8</v>
       </c>
-      <c r="H113" s="46" t="n">
+      <c r="H113" s="44" t="n">
         <f aca="false">H112+H111</f>
-        <v>-210.091091046031</v>
-      </c>
-      <c r="I113" s="46" t="n">
+        <v>-210.095167646701</v>
+      </c>
+      <c r="I113" s="44" t="n">
         <f aca="false">I112+I111</f>
-        <v>-359.875536943741</v>
-      </c>
-      <c r="J113" s="46" t="n">
+        <v>-359.882446244934</v>
+      </c>
+      <c r="J113" s="44" t="n">
         <f aca="false">J112+J111</f>
-        <v>-483.786203138412</v>
+        <v>-483.794438638808</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="C114" s="44" t="n">
+      <c r="C114" s="42" t="n">
         <f aca="false">Historical!C114</f>
         <v>161.8</v>
       </c>
-      <c r="D114" s="44" t="n">
+      <c r="D114" s="42" t="n">
         <f aca="false">Historical!D114</f>
         <v>-7</v>
       </c>
-      <c r="E114" s="44" t="n">
+      <c r="E114" s="42" t="n">
         <f aca="false">Historical!E114</f>
         <v>3.7</v>
       </c>
-      <c r="F114" s="44" t="n">
+      <c r="F114" s="42" t="n">
         <f aca="false">Historical!F114</f>
         <v>-70</v>
       </c>
-      <c r="G114" s="44" t="n">
+      <c r="G114" s="42" t="n">
         <f aca="false">Historical!G114</f>
         <v>-54.5</v>
       </c>
-      <c r="H114" s="47"/>
-      <c r="I114" s="47"/>
-      <c r="J114" s="47"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
+      <c r="J114" s="45"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="21" t="s">
@@ -10334,23 +10316,23 @@
       <c r="A117" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="C117" s="44" t="n">
+      <c r="C117" s="42" t="n">
         <f aca="false">Historical!C117</f>
         <v>-54.3</v>
       </c>
-      <c r="D117" s="44" t="n">
+      <c r="D117" s="42" t="n">
         <f aca="false">Historical!D117</f>
         <v>-103.3</v>
       </c>
-      <c r="E117" s="44" t="n">
+      <c r="E117" s="42" t="n">
         <f aca="false">Historical!E117</f>
         <v>-198.1</v>
       </c>
-      <c r="F117" s="44" t="n">
+      <c r="F117" s="42" t="n">
         <f aca="false">Historical!F117</f>
         <v>-240.9</v>
       </c>
-      <c r="G117" s="44" t="n">
+      <c r="G117" s="42" t="n">
         <f aca="false">Historical!G117</f>
         <v>-285.4</v>
       </c>
@@ -10371,37 +10353,37 @@
       <c r="A118" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="C118" s="44" t="n">
+      <c r="C118" s="42" t="n">
         <f aca="false">Historical!C118</f>
         <v>182.2</v>
       </c>
-      <c r="D118" s="44" t="n">
+      <c r="D118" s="42" t="n">
         <f aca="false">Historical!D118</f>
         <v>96.9</v>
       </c>
-      <c r="E118" s="44" t="n">
+      <c r="E118" s="42" t="n">
         <f aca="false">Historical!E118</f>
         <v>65.1</v>
       </c>
-      <c r="F118" s="44" t="n">
+      <c r="F118" s="42" t="n">
         <f aca="false">Historical!F118</f>
         <v>21</v>
       </c>
-      <c r="G118" s="44" t="n">
+      <c r="G118" s="42" t="n">
         <f aca="false">Historical!G118</f>
         <v>-11.7</v>
       </c>
       <c r="H118" s="28" t="n">
         <f aca="false">H97+H117+H109</f>
-        <v>-210.580091046031</v>
+        <v>-210.584167646701</v>
       </c>
       <c r="I118" s="28" t="n">
         <f aca="false">I97+I117+I109</f>
-        <v>-78.0672258977102</v>
+        <v>-78.0700585982335</v>
       </c>
       <c r="J118" s="28" t="n">
         <f aca="false">J97+J117+J109</f>
-        <v>-50.759101794671</v>
+        <v>-50.7604279938735</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10422,511 +10404,511 @@
       <c r="A121" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="C121" s="44" t="n">
+      <c r="C121" s="42" t="n">
         <f aca="false">Historical!C121</f>
         <v>117.5</v>
       </c>
-      <c r="D121" s="44" t="n">
+      <c r="D121" s="42" t="n">
         <f aca="false">Historical!D121</f>
         <v>120.3</v>
       </c>
-      <c r="E121" s="44" t="n">
+      <c r="E121" s="42" t="n">
         <f aca="false">Historical!E121</f>
         <v>142.5</v>
       </c>
-      <c r="F121" s="44" t="n">
+      <c r="F121" s="42" t="n">
         <f aca="false">Historical!F121</f>
         <v>153.4</v>
       </c>
-      <c r="G121" s="44" t="n">
+      <c r="G121" s="42" t="n">
         <f aca="false">Historical!G121</f>
         <v>122.2</v>
       </c>
-      <c r="H121" s="47"/>
-      <c r="I121" s="47"/>
-      <c r="J121" s="47"/>
+      <c r="H121" s="45"/>
+      <c r="I121" s="45"/>
+      <c r="J121" s="45"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="C122" s="44" t="n">
+      <c r="C122" s="42" t="n">
         <f aca="false">Historical!C122</f>
         <v>4.5</v>
       </c>
-      <c r="D122" s="44" t="n">
+      <c r="D122" s="42" t="n">
         <f aca="false">Historical!D122</f>
         <v>4.7</v>
       </c>
-      <c r="E122" s="44" t="n">
+      <c r="E122" s="42" t="n">
         <f aca="false">Historical!E122</f>
         <v>3.9</v>
       </c>
-      <c r="F122" s="44" t="n">
+      <c r="F122" s="42" t="n">
         <f aca="false">Historical!F122</f>
         <v>4.2</v>
       </c>
-      <c r="G122" s="44" t="n">
+      <c r="G122" s="42" t="n">
         <f aca="false">Historical!G122</f>
         <v>4.7</v>
       </c>
-      <c r="H122" s="47"/>
-      <c r="I122" s="47"/>
-      <c r="J122" s="47"/>
+      <c r="H122" s="45"/>
+      <c r="I122" s="45"/>
+      <c r="J122" s="45"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="C123" s="44" t="n">
+      <c r="C123" s="42" t="n">
         <f aca="false">Historical!C123</f>
         <v>54.2</v>
       </c>
-      <c r="D123" s="44" t="n">
+      <c r="D123" s="42" t="n">
         <f aca="false">Historical!D123</f>
         <v>58</v>
       </c>
-      <c r="E123" s="44" t="n">
+      <c r="E123" s="42" t="n">
         <f aca="false">Historical!E123</f>
         <v>66.6</v>
       </c>
-      <c r="F123" s="44" t="n">
+      <c r="F123" s="42" t="n">
         <f aca="false">Historical!F123</f>
         <v>76.6</v>
       </c>
-      <c r="G123" s="44" t="n">
+      <c r="G123" s="42" t="n">
         <f aca="false">Historical!G123</f>
         <v>90.7</v>
       </c>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="45"/>
+      <c r="J123" s="45"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="C124" s="44" t="n">
+      <c r="C124" s="42" t="n">
         <f aca="false">Historical!C124</f>
         <v>48.7</v>
       </c>
-      <c r="D124" s="44" t="n">
+      <c r="D124" s="42" t="n">
         <f aca="false">Historical!D124</f>
         <v>52.8</v>
       </c>
-      <c r="E124" s="44" t="n">
+      <c r="E124" s="42" t="n">
         <f aca="false">Historical!E124</f>
         <v>54.5</v>
       </c>
-      <c r="F124" s="44" t="n">
+      <c r="F124" s="42" t="n">
         <f aca="false">Historical!F124</f>
         <v>59.2</v>
       </c>
-      <c r="G124" s="44" t="n">
+      <c r="G124" s="42" t="n">
         <f aca="false">Historical!G124</f>
         <v>65.2</v>
       </c>
-      <c r="H124" s="47"/>
-      <c r="I124" s="47"/>
-      <c r="J124" s="47"/>
+      <c r="H124" s="45"/>
+      <c r="I124" s="45"/>
+      <c r="J124" s="45"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C125" s="44" t="n">
+      <c r="C125" s="42" t="n">
         <f aca="false">Historical!C125</f>
         <v>-1.9</v>
       </c>
-      <c r="D125" s="44" t="n">
+      <c r="D125" s="42" t="n">
         <f aca="false">Historical!D125</f>
         <v>1.2</v>
       </c>
-      <c r="E125" s="44" t="n">
+      <c r="E125" s="42" t="n">
         <f aca="false">Historical!E125</f>
         <v>1.4</v>
       </c>
-      <c r="F125" s="44" t="n">
+      <c r="F125" s="42" t="n">
         <f aca="false">Historical!F125</f>
         <v>2.9</v>
       </c>
-      <c r="G125" s="44" t="n">
+      <c r="G125" s="42" t="n">
         <f aca="false">Historical!G125</f>
         <v>3.9</v>
       </c>
-      <c r="H125" s="47"/>
-      <c r="I125" s="47"/>
-      <c r="J125" s="47"/>
+      <c r="H125" s="45"/>
+      <c r="I125" s="45"/>
+      <c r="J125" s="45"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="C126" s="44" t="n">
+      <c r="C126" s="42" t="n">
         <f aca="false">Historical!C126</f>
         <v>-1.6</v>
       </c>
-      <c r="D126" s="44" t="n">
+      <c r="D126" s="42" t="n">
         <f aca="false">Historical!D126</f>
         <v>0</v>
       </c>
-      <c r="E126" s="44" t="n">
+      <c r="E126" s="42" t="n">
         <f aca="false">Historical!E126</f>
         <v>2.5</v>
       </c>
-      <c r="F126" s="44" t="n">
+      <c r="F126" s="42" t="n">
         <f aca="false">Historical!F126</f>
         <v>2.1</v>
       </c>
-      <c r="G126" s="44" t="n">
+      <c r="G126" s="42" t="n">
         <f aca="false">Historical!G126</f>
         <v>3</v>
       </c>
-      <c r="H126" s="47"/>
-      <c r="I126" s="47"/>
-      <c r="J126" s="47"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="45"/>
+      <c r="J126" s="45"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="C127" s="44" t="n">
+      <c r="C127" s="42" t="n">
         <f aca="false">Historical!C127</f>
         <v>0.9</v>
       </c>
-      <c r="D127" s="44" t="n">
+      <c r="D127" s="42" t="n">
         <f aca="false">Historical!D127</f>
         <v>1</v>
       </c>
-      <c r="E127" s="44" t="n">
+      <c r="E127" s="42" t="n">
         <f aca="false">Historical!E127</f>
         <v>2</v>
       </c>
-      <c r="F127" s="44" t="n">
+      <c r="F127" s="42" t="n">
         <f aca="false">Historical!F127</f>
         <v>-11.8</v>
       </c>
-      <c r="G127" s="44" t="n">
+      <c r="G127" s="42" t="n">
         <f aca="false">Historical!G127</f>
         <v>1.7</v>
       </c>
-      <c r="H127" s="47"/>
-      <c r="I127" s="47"/>
-      <c r="J127" s="47"/>
+      <c r="H127" s="45"/>
+      <c r="I127" s="45"/>
+      <c r="J127" s="45"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="C128" s="44" t="n">
+      <c r="C128" s="42" t="n">
         <f aca="false">Historical!C128</f>
         <v>-0.5</v>
       </c>
-      <c r="D128" s="44" t="n">
+      <c r="D128" s="42" t="n">
         <f aca="false">Historical!D128</f>
         <v>-0.4</v>
       </c>
-      <c r="E128" s="44" t="n">
+      <c r="E128" s="42" t="n">
         <f aca="false">Historical!E128</f>
         <v>-0.5</v>
       </c>
-      <c r="F128" s="44" t="n">
+      <c r="F128" s="42" t="n">
         <f aca="false">Historical!F128</f>
         <v>-0.5</v>
       </c>
-      <c r="G128" s="44" t="n">
+      <c r="G128" s="42" t="n">
         <f aca="false">Historical!G128</f>
         <v>-0.5</v>
       </c>
-      <c r="H128" s="47"/>
-      <c r="I128" s="47"/>
-      <c r="J128" s="47"/>
+      <c r="H128" s="45"/>
+      <c r="I128" s="45"/>
+      <c r="J128" s="45"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="C129" s="44" t="n">
+      <c r="C129" s="42" t="n">
         <f aca="false">Historical!C129</f>
         <v>2.2</v>
       </c>
-      <c r="D129" s="44" t="n">
+      <c r="D129" s="42" t="n">
         <f aca="false">Historical!D129</f>
         <v>3.6</v>
       </c>
-      <c r="E129" s="44" t="n">
+      <c r="E129" s="42" t="n">
         <f aca="false">Historical!E129</f>
         <v>4.6</v>
       </c>
-      <c r="F129" s="44" t="n">
+      <c r="F129" s="42" t="n">
         <f aca="false">Historical!F129</f>
         <v>4.5</v>
       </c>
-      <c r="G129" s="44" t="n">
+      <c r="G129" s="42" t="n">
         <f aca="false">Historical!G129</f>
         <v>1.5</v>
       </c>
-      <c r="H129" s="47"/>
-      <c r="I129" s="47"/>
-      <c r="J129" s="47"/>
+      <c r="H129" s="45"/>
+      <c r="I129" s="45"/>
+      <c r="J129" s="45"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C130" s="44" t="n">
+      <c r="C130" s="42" t="n">
         <f aca="false">Historical!C130</f>
         <v>0</v>
       </c>
-      <c r="D130" s="44" t="n">
+      <c r="D130" s="42" t="n">
         <f aca="false">Historical!D130</f>
         <v>0</v>
       </c>
-      <c r="E130" s="44" t="n">
+      <c r="E130" s="42" t="n">
         <f aca="false">Historical!E130</f>
         <v>-6.1</v>
       </c>
-      <c r="F130" s="44" t="n">
+      <c r="F130" s="42" t="n">
         <f aca="false">Historical!F130</f>
         <v>-8.1</v>
       </c>
-      <c r="G130" s="44" t="n">
+      <c r="G130" s="42" t="n">
         <f aca="false">Historical!G130</f>
         <v>-1.8</v>
       </c>
-      <c r="H130" s="47"/>
-      <c r="I130" s="47"/>
-      <c r="J130" s="47"/>
+      <c r="H130" s="45"/>
+      <c r="I130" s="45"/>
+      <c r="J130" s="45"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="44" t="n">
+      <c r="C131" s="42" t="n">
         <f aca="false">Historical!C131</f>
         <v>7.6</v>
       </c>
-      <c r="D131" s="44" t="n">
+      <c r="D131" s="42" t="n">
         <f aca="false">Historical!D131</f>
         <v>6.1</v>
       </c>
-      <c r="E131" s="44" t="n">
+      <c r="E131" s="42" t="n">
         <f aca="false">Historical!E131</f>
         <v>10.1</v>
       </c>
-      <c r="F131" s="44" t="n">
+      <c r="F131" s="42" t="n">
         <f aca="false">Historical!F131</f>
         <v>13.6</v>
       </c>
-      <c r="G131" s="44" t="n">
+      <c r="G131" s="42" t="n">
         <f aca="false">Historical!G131</f>
         <v>18.1</v>
       </c>
-      <c r="H131" s="47"/>
-      <c r="I131" s="47"/>
-      <c r="J131" s="47"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="45"/>
+      <c r="J131" s="45"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="C132" s="44" t="n">
+      <c r="C132" s="42" t="n">
         <f aca="false">Historical!C132</f>
         <v>28.1</v>
       </c>
-      <c r="D132" s="44" t="n">
+      <c r="D132" s="42" t="n">
         <f aca="false">Historical!D132</f>
         <v>28</v>
       </c>
-      <c r="E132" s="44" t="n">
+      <c r="E132" s="42" t="n">
         <f aca="false">Historical!E132</f>
         <v>45.8</v>
       </c>
-      <c r="F132" s="44" t="n">
+      <c r="F132" s="42" t="n">
         <f aca="false">Historical!F132</f>
         <v>50.5</v>
       </c>
-      <c r="G132" s="44" t="n">
+      <c r="G132" s="42" t="n">
         <f aca="false">Historical!G132</f>
         <v>45.2</v>
       </c>
-      <c r="H132" s="47"/>
-      <c r="I132" s="47"/>
-      <c r="J132" s="47"/>
+      <c r="H132" s="45"/>
+      <c r="I132" s="45"/>
+      <c r="J132" s="45"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="C133" s="44" t="n">
+      <c r="C133" s="42" t="n">
         <f aca="false">Historical!C133</f>
         <v>-5.4</v>
       </c>
-      <c r="D133" s="44" t="n">
+      <c r="D133" s="42" t="n">
         <f aca="false">Historical!D133</f>
         <v>-12.7</v>
       </c>
-      <c r="E133" s="44" t="n">
+      <c r="E133" s="42" t="n">
         <f aca="false">Historical!E133</f>
         <v>-8.2</v>
       </c>
-      <c r="F133" s="44" t="n">
+      <c r="F133" s="42" t="n">
         <f aca="false">Historical!F133</f>
         <v>-6.4</v>
       </c>
-      <c r="G133" s="44" t="n">
+      <c r="G133" s="42" t="n">
         <f aca="false">Historical!G133</f>
         <v>-0.4</v>
       </c>
-      <c r="H133" s="47"/>
-      <c r="I133" s="47"/>
-      <c r="J133" s="47"/>
+      <c r="H133" s="45"/>
+      <c r="I133" s="45"/>
+      <c r="J133" s="45"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="C134" s="44" t="n">
+      <c r="C134" s="42" t="n">
         <f aca="false">Historical!C134</f>
         <v>1.8</v>
       </c>
-      <c r="D134" s="44" t="n">
+      <c r="D134" s="42" t="n">
         <f aca="false">Historical!D134</f>
         <v>-12.4</v>
       </c>
-      <c r="E134" s="44" t="n">
+      <c r="E134" s="42" t="n">
         <f aca="false">Historical!E134</f>
         <v>-3.6</v>
       </c>
-      <c r="F134" s="44" t="n">
+      <c r="F134" s="42" t="n">
         <f aca="false">Historical!F134</f>
         <v>-8.1</v>
       </c>
-      <c r="G134" s="44" t="n">
+      <c r="G134" s="42" t="n">
         <f aca="false">Historical!G134</f>
         <v>-7.4</v>
       </c>
-      <c r="H134" s="47"/>
-      <c r="I134" s="47"/>
-      <c r="J134" s="47"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="45"/>
+      <c r="J134" s="45"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C135" s="44" t="n">
+      <c r="C135" s="42" t="n">
         <f aca="false">Historical!C135</f>
         <v>58.9</v>
       </c>
-      <c r="D135" s="44" t="n">
+      <c r="D135" s="42" t="n">
         <f aca="false">Historical!D135</f>
         <v>30.8</v>
       </c>
-      <c r="E135" s="44" t="n">
+      <c r="E135" s="42" t="n">
         <f aca="false">Historical!E135</f>
         <v>18</v>
       </c>
-      <c r="F135" s="44" t="n">
+      <c r="F135" s="42" t="n">
         <f aca="false">Historical!F135</f>
         <v>24.9</v>
       </c>
-      <c r="G135" s="44" t="n">
+      <c r="G135" s="42" t="n">
         <f aca="false">Historical!G135</f>
         <v>31.6</v>
       </c>
-      <c r="H135" s="47"/>
-      <c r="I135" s="47"/>
-      <c r="J135" s="47"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="45"/>
+      <c r="J135" s="45"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="C136" s="44" t="n">
+      <c r="C136" s="42" t="n">
         <f aca="false">Historical!C136</f>
         <v>-0.4</v>
       </c>
-      <c r="D136" s="44" t="n">
+      <c r="D136" s="42" t="n">
         <f aca="false">Historical!D136</f>
         <v>-0.7</v>
       </c>
-      <c r="E136" s="44" t="n">
+      <c r="E136" s="42" t="n">
         <f aca="false">Historical!E136</f>
         <v>-0.5</v>
       </c>
-      <c r="F136" s="44" t="n">
+      <c r="F136" s="42" t="n">
         <f aca="false">Historical!F136</f>
         <v>0.1</v>
       </c>
-      <c r="G136" s="44" t="n">
+      <c r="G136" s="42" t="n">
         <f aca="false">Historical!G136</f>
         <v>6</v>
       </c>
-      <c r="H136" s="47"/>
-      <c r="I136" s="47"/>
-      <c r="J136" s="47"/>
+      <c r="H136" s="45"/>
+      <c r="I136" s="45"/>
+      <c r="J136" s="45"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C137" s="44" t="n">
+      <c r="C137" s="42" t="n">
         <f aca="false">Historical!C137</f>
         <v>-2.5</v>
       </c>
-      <c r="D137" s="44" t="n">
+      <c r="D137" s="42" t="n">
         <f aca="false">Historical!D137</f>
         <v>-8</v>
       </c>
-      <c r="E137" s="44" t="n">
+      <c r="E137" s="42" t="n">
         <f aca="false">Historical!E137</f>
         <v>0</v>
       </c>
-      <c r="F137" s="44" t="n">
+      <c r="F137" s="42" t="n">
         <f aca="false">Historical!F137</f>
         <v>-4.5</v>
       </c>
-      <c r="G137" s="44" t="n">
+      <c r="G137" s="42" t="n">
         <f aca="false">Historical!G137</f>
         <v>0</v>
       </c>
-      <c r="H137" s="47"/>
-      <c r="I137" s="47"/>
-      <c r="J137" s="47"/>
+      <c r="H137" s="45"/>
+      <c r="I137" s="45"/>
+      <c r="J137" s="45"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="C138" s="44" t="n">
+      <c r="C138" s="42" t="n">
         <f aca="false">Historical!C138</f>
         <v>312.1</v>
       </c>
-      <c r="D138" s="44" t="n">
+      <c r="D138" s="42" t="n">
         <f aca="false">Historical!D138</f>
         <v>272.3</v>
       </c>
-      <c r="E138" s="44" t="n">
+      <c r="E138" s="42" t="n">
         <f aca="false">Historical!E138</f>
         <v>333</v>
       </c>
-      <c r="F138" s="44" t="n">
+      <c r="F138" s="42" t="n">
         <f aca="false">Historical!F138</f>
         <v>352.6</v>
       </c>
-      <c r="G138" s="44" t="n">
+      <c r="G138" s="42" t="n">
         <f aca="false">Historical!G138</f>
         <v>383.7</v>
       </c>
-      <c r="H138" s="46" t="n">
+      <c r="H138" s="44" t="n">
         <f aca="false">SUM(H121:H137)</f>
         <v>0</v>
       </c>
-      <c r="I138" s="46" t="n">
+      <c r="I138" s="44" t="n">
         <f aca="false">SUM(I121:I137)</f>
         <v>0</v>
       </c>
-      <c r="J138" s="46" t="n">
+      <c r="J138" s="44" t="n">
         <f aca="false">SUM(J121:J137)</f>
         <v>0</v>
       </c>
@@ -10935,23 +10917,23 @@
       <c r="A139" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="C139" s="44" t="n">
+      <c r="C139" s="42" t="n">
         <f aca="false">Historical!C139</f>
         <v>107.4</v>
       </c>
-      <c r="D139" s="44" t="n">
+      <c r="D139" s="42" t="n">
         <f aca="false">Historical!D139</f>
         <v>115.5</v>
       </c>
-      <c r="E139" s="44" t="n">
+      <c r="E139" s="42" t="n">
         <f aca="false">Historical!E139</f>
         <v>125</v>
       </c>
-      <c r="F139" s="44" t="n">
+      <c r="F139" s="42" t="n">
         <f aca="false">Historical!F139</f>
         <v>140</v>
       </c>
-      <c r="G139" s="44" t="n">
+      <c r="G139" s="42" t="n">
         <f aca="false">Historical!G139</f>
         <v>160.6</v>
       </c>
@@ -11059,15 +11041,15 @@
       </c>
       <c r="H146" s="28" t="n">
         <f aca="false">-(G66+G71)*H42/G42</f>
-        <v>463.110192578675</v>
+        <v>463.06036499766</v>
       </c>
       <c r="I146" s="28" t="n">
         <f aca="false">-(H66+H71)*I42/H42</f>
-        <v>477.054203851574</v>
+        <v>476.95217594759</v>
       </c>
       <c r="J146" s="28" t="n">
         <f aca="false">-(I66+I71)*J42/I42</f>
-        <v>490.998215124472</v>
+        <v>490.84398689752</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11080,11 +11062,11 @@
       </c>
       <c r="I147" s="28" t="n">
         <f aca="false">H54*Drivers!$D$29</f>
-        <v>72.2876092062001</v>
+        <v>72.2798315395414</v>
       </c>
       <c r="J147" s="28" t="n">
         <f aca="false">I54*Drivers!$E$29</f>
-        <v>74.464152184124</v>
+        <v>74.4482264857277</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11096,15 +11078,15 @@
       </c>
       <c r="H148" s="28" t="n">
         <f aca="false">H54-G54+H147</f>
-        <v>82.4312306247064</v>
+        <v>82.3854796443613</v>
       </c>
       <c r="I148" s="28" t="n">
         <f aca="false">I54-H54+I147</f>
-        <v>85.0908031939878</v>
+        <v>85.0350959288722</v>
       </c>
       <c r="J148" s="28" t="n">
         <f aca="false">J54-I54+J147</f>
-        <v>87.2673461719117</v>
+        <v>87.2034908750585</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11116,15 +11098,15 @@
       </c>
       <c r="H149" s="28" t="n">
         <f aca="false">-(G66+G71)+H148-H146</f>
-        <v>69.121038046031</v>
+        <v>69.125114646701</v>
       </c>
       <c r="I149" s="28" t="n">
         <f aca="false">-(H66+H71)+I148-I146</f>
-        <v>71.1467919210897</v>
+        <v>71.1432849789424</v>
       </c>
       <c r="J149" s="28" t="n">
         <f aca="false">-(I66+I71)+J148-J146</f>
-        <v>73.3233348990137</v>
+        <v>73.3116799251287</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11137,11 +11119,11 @@
       </c>
       <c r="I150" s="28" t="n">
         <f aca="false">-(H66+H71)*Drivers!$D$30</f>
-        <v>18.0612975105683</v>
+        <v>18.0593542349088</v>
       </c>
       <c r="J150" s="28" t="n">
         <f aca="false">-(I66+I71)*Drivers!$E$30</f>
-        <v>18.6051139502114</v>
+        <v>18.601134861956</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11256,18 +11238,18 @@
       <c r="B157" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="G157" s="50" t="n">
+      <c r="G157" s="48" t="n">
         <v>0.69</v>
       </c>
-      <c r="H157" s="35" t="n">
+      <c r="H157" s="33" t="n">
         <f aca="false">Drivers!$C$17</f>
         <v>0.7038</v>
       </c>
-      <c r="I157" s="35" t="n">
+      <c r="I157" s="33" t="n">
         <f aca="false">Drivers!$D$17</f>
         <v>0.717876</v>
       </c>
-      <c r="J157" s="35" t="n">
+      <c r="J157" s="33" t="n">
         <f aca="false">Drivers!$E$17</f>
         <v>0.73223352</v>
       </c>
@@ -11327,40 +11309,40 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="34" t="s">
         <v>325</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="34" t="s">
         <v>329</v>
       </c>
     </row>
@@ -11425,31 +11407,31 @@
       <c r="B7" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="J7" s="33" t="n">
+      <c r="J7" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="K7" s="33" t="n">
+      <c r="K7" s="31" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" s="16" t="s">
@@ -11463,31 +11445,31 @@
       <c r="B8" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="31" t="n">
         <v>0.026</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="31" t="n">
         <v>0.015</v>
       </c>
-      <c r="G8" s="33" t="n">
+      <c r="G8" s="31" t="n">
         <v>0.035</v>
       </c>
-      <c r="H8" s="33" t="n">
+      <c r="H8" s="31" t="n">
         <v>0.005</v>
       </c>
-      <c r="I8" s="33" t="n">
+      <c r="I8" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="J8" s="33" t="n">
+      <c r="J8" s="31" t="n">
         <v>0.005</v>
       </c>
-      <c r="K8" s="33" t="n">
+      <c r="K8" s="31" t="n">
         <v>0.05</v>
       </c>
       <c r="L8" s="16" t="s">
@@ -11501,31 +11483,31 @@
       <c r="B9" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="J9" s="33" t="n">
+      <c r="J9" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="K9" s="33" t="n">
+      <c r="K9" s="31" t="n">
         <v>0.95</v>
       </c>
       <c r="L9" s="16" t="s">
@@ -11539,31 +11521,31 @@
       <c r="B10" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="31" t="n">
         <v>0.06</v>
       </c>
-      <c r="G10" s="33" t="n">
+      <c r="G10" s="31" t="n">
         <v>0.14</v>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="I10" s="33" t="n">
+      <c r="I10" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="J10" s="33" t="n">
+      <c r="J10" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="K10" s="33" t="n">
+      <c r="K10" s="31" t="n">
         <v>0.12</v>
       </c>
       <c r="L10" s="16" t="s">
@@ -11577,31 +11559,31 @@
       <c r="B11" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="31" t="n">
         <v>0.088</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="31" t="n">
         <v>0.09</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="31" t="n">
         <v>0.093</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="31" t="n">
         <v>0.082</v>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="31" t="n">
         <v>0.094</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="I11" s="33" t="n">
+      <c r="I11" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="J11" s="33" t="n">
+      <c r="J11" s="31" t="n">
         <v>0.083</v>
       </c>
-      <c r="K11" s="33" t="n">
+      <c r="K11" s="31" t="n">
         <v>0.103</v>
       </c>
       <c r="L11" s="16" t="s">
@@ -11637,13 +11619,13 @@
       <c r="B13" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="31" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="31" t="n">
         <v>0.0833333333333333</v>
       </c>
       <c r="L13" s="16" t="s">
@@ -11657,13 +11639,13 @@
       <c r="B14" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="31" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="31" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="31" t="n">
         <v>0.25</v>
       </c>
       <c r="L14" s="16" t="s">
@@ -11715,13 +11697,13 @@
       <c r="B16" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="31" t="n">
         <v>0.02</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="31" t="n">
         <v>0.02</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="31" t="n">
         <v>0.02</v>
       </c>
       <c r="L16" s="16" t="s">
@@ -11735,15 +11717,15 @@
       <c r="B17" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">0.69*(1+C16)</f>
         <v>0.7038</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="33" t="n">
         <f aca="false">C17*(1+D16)</f>
         <v>0.717876</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="33" t="n">
         <f aca="false">D17*(1+E16)</f>
         <v>0.73223352</v>
       </c>
@@ -11758,31 +11740,31 @@
       <c r="B18" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="E18" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="F18" s="33" t="n">
+      <c r="F18" s="31" t="n">
         <v>0.255</v>
       </c>
-      <c r="G18" s="33" t="n">
+      <c r="G18" s="31" t="n">
         <v>0.27</v>
       </c>
-      <c r="H18" s="33" t="n">
+      <c r="H18" s="31" t="n">
         <v>0.255</v>
       </c>
-      <c r="I18" s="33" t="n">
+      <c r="I18" s="31" t="n">
         <v>0.27</v>
       </c>
-      <c r="J18" s="33" t="n">
+      <c r="J18" s="31" t="n">
         <v>0.255</v>
       </c>
-      <c r="K18" s="33" t="n">
+      <c r="K18" s="31" t="n">
         <v>0.27</v>
       </c>
       <c r="L18" s="16" t="s">
@@ -11812,13 +11794,13 @@
       <c r="B21" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="31" t="n">
         <v>0.615</v>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="31" t="n">
         <v>0.615</v>
       </c>
-      <c r="E21" s="33" t="n">
+      <c r="E21" s="31" t="n">
         <v>0.615</v>
       </c>
       <c r="L21" s="16" t="s">
@@ -11832,13 +11814,13 @@
       <c r="B22" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C22" s="31" t="n">
         <v>0.047</v>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="31" t="n">
         <v>0.047</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="31" t="n">
         <v>0.047</v>
       </c>
       <c r="L22" s="16" t="s">
@@ -11912,13 +11894,13 @@
       <c r="B26" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C26" s="31" t="n">
         <v>0.135</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="31" t="n">
         <v>0.135</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="31" t="n">
         <v>0.135</v>
       </c>
       <c r="L26" s="16" t="s">
@@ -11932,13 +11914,13 @@
       <c r="B27" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="31" t="n">
         <v>0.08</v>
       </c>
       <c r="L27" s="16" t="s">
@@ -11952,13 +11934,13 @@
       <c r="B28" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C28" s="33" t="n">
+      <c r="C28" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="D28" s="33" t="n">
+      <c r="D28" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="31" t="n">
         <v>0.18</v>
       </c>
       <c r="L28" s="16" t="s">
@@ -11972,13 +11954,13 @@
       <c r="B29" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C29" s="33" t="n">
+      <c r="C29" s="31" t="n">
         <v>0.17</v>
       </c>
-      <c r="D29" s="33" t="n">
+      <c r="D29" s="31" t="n">
         <v>0.17</v>
       </c>
-      <c r="E29" s="33" t="n">
+      <c r="E29" s="31" t="n">
         <v>0.17</v>
       </c>
       <c r="L29" s="16" t="s">
@@ -11992,13 +11974,13 @@
       <c r="B30" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="31" t="n">
         <v>0.039</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="31" t="n">
         <v>0.039</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="31" t="n">
         <v>0.039</v>
       </c>
       <c r="L30" s="16" t="s">
@@ -12012,13 +11994,13 @@
       <c r="B31" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C31" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="D31" s="33" t="n">
+      <c r="D31" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="E31" s="33" t="n">
+      <c r="E31" s="31" t="n">
         <v>0.03</v>
       </c>
       <c r="L31" s="16" t="s">
@@ -12032,13 +12014,13 @@
       <c r="B32" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C32" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="31" t="n">
         <v>0.05</v>
       </c>
       <c r="L32" s="16" t="s">
@@ -12052,13 +12034,13 @@
       <c r="B33" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C33" s="33" t="n">
+      <c r="C33" s="31" t="n">
         <v>0.11</v>
       </c>
-      <c r="D33" s="33" t="n">
+      <c r="D33" s="31" t="n">
         <v>0.11</v>
       </c>
-      <c r="E33" s="33" t="n">
+      <c r="E33" s="31" t="n">
         <v>0.11</v>
       </c>
       <c r="L33" s="16" t="s">
@@ -12092,13 +12074,13 @@
       <c r="B35" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C35" s="33" t="n">
+      <c r="C35" s="31" t="n">
         <v>0.139</v>
       </c>
-      <c r="D35" s="33" t="n">
+      <c r="D35" s="31" t="n">
         <v>0.139</v>
       </c>
-      <c r="E35" s="33" t="n">
+      <c r="E35" s="31" t="n">
         <v>0.139</v>
       </c>
       <c r="L35" s="16" t="s">
@@ -12128,11 +12110,11 @@
       <c r="B38" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="C38" s="51" t="n">
+      <c r="C38" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
       <c r="L38" s="16" t="s">
         <v>394</v>
       </c>
@@ -12144,11 +12126,11 @@
       <c r="B39" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="C39" s="51" t="n">
+      <c r="C39" s="49" t="n">
         <v>0.3</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
       <c r="L39" s="16" t="s">
         <v>396</v>
       </c>
@@ -12170,20 +12152,20 @@
       <c r="L41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="36" t="s">
+      <c r="A42" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36" t="s">
+      <c r="B42" s="34"/>
+      <c r="C42" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="E42" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="36" t="s">
+      <c r="F42" s="34" t="s">
         <v>89</v>
       </c>
     </row>
@@ -12191,19 +12173,19 @@
       <c r="A43" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="C43" s="39" t="n">
+      <c r="C43" s="37" t="n">
         <f aca="false">Historical!D7/Historical!C7-1</f>
         <v>0.23021875254127</v>
       </c>
-      <c r="D43" s="39" t="n">
+      <c r="D43" s="37" t="n">
         <f aca="false">Historical!E7/Historical!D7-1</f>
         <v>0.196192490745637</v>
       </c>
-      <c r="E43" s="39" t="n">
+      <c r="E43" s="37" t="n">
         <f aca="false">Historical!F7/Historical!E7-1</f>
         <v>0.113174182139699</v>
       </c>
-      <c r="F43" s="39" t="n">
+      <c r="F43" s="37" t="n">
         <f aca="false">Historical!G7/Historical!F7-1</f>
         <v>0.0679110405083399</v>
       </c>
@@ -12212,19 +12194,19 @@
       <c r="A44" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="C44" s="39" t="n">
+      <c r="C44" s="37" t="n">
         <f aca="false">Historical!D47</f>
         <v>0.178</v>
       </c>
-      <c r="D44" s="39" t="n">
+      <c r="D44" s="37" t="n">
         <f aca="false">Historical!E47</f>
         <v>0.137</v>
       </c>
-      <c r="E44" s="39" t="n">
+      <c r="E44" s="37" t="n">
         <f aca="false">Historical!F47</f>
         <v>0.055</v>
       </c>
-      <c r="F44" s="39" t="n">
+      <c r="F44" s="37" t="n">
         <f aca="false">Historical!G47</f>
         <v>0.024</v>
       </c>
@@ -12233,19 +12215,19 @@
       <c r="A45" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="C45" s="39" t="n">
+      <c r="C45" s="37" t="n">
         <f aca="false">Historical!D37/Historical!C37-1</f>
         <v>0.220532319391635</v>
       </c>
-      <c r="D45" s="39" t="n">
+      <c r="D45" s="37" t="n">
         <f aca="false">Historical!E37/Historical!D37-1</f>
         <v>0.238006230529595</v>
       </c>
-      <c r="E45" s="39" t="n">
+      <c r="E45" s="37" t="n">
         <f aca="false">Historical!F37/Historical!E37-1</f>
         <v>0.171112229491696</v>
       </c>
-      <c r="F45" s="39" t="n">
+      <c r="F45" s="37" t="n">
         <f aca="false">Historical!G37/Historical!F37-1</f>
         <v>0.0915341641598626</v>
       </c>
@@ -12254,19 +12236,19 @@
       <c r="A46" s="23" t="s">
         <v>361</v>
       </c>
-      <c r="C46" s="39" t="n">
+      <c r="C46" s="37" t="n">
         <f aca="false">1+Historical!D8/Historical!D7</f>
         <v>0.620240613432047</v>
       </c>
-      <c r="D46" s="39" t="n">
+      <c r="D46" s="37" t="n">
         <f aca="false">1+Historical!E8/Historical!E7</f>
         <v>0.607371794871795</v>
       </c>
-      <c r="E46" s="39" t="n">
+      <c r="E46" s="37" t="n">
         <f aca="false">1+Historical!F8/Historical!F7</f>
         <v>0.617355043685465</v>
       </c>
-      <c r="F46" s="39" t="n">
+      <c r="F46" s="37" t="n">
         <f aca="false">1+Historical!G8/Historical!G7</f>
         <v>0.614587207140201</v>
       </c>
@@ -12275,19 +12257,19 @@
       <c r="A47" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="39" t="n">
+      <c r="C47" s="37" t="n">
         <f aca="false">Historical!D26</f>
         <v>0.102062400846113</v>
       </c>
-      <c r="D47" s="39" t="n">
+      <c r="D47" s="37" t="n">
         <f aca="false">Historical!E26</f>
         <v>0.0948828470380194</v>
       </c>
-      <c r="E47" s="39" t="n">
+      <c r="E47" s="37" t="n">
         <f aca="false">Historical!F26</f>
         <v>0.0969519459888801</v>
       </c>
-      <c r="F47" s="39" t="n">
+      <c r="F47" s="37" t="n">
         <f aca="false">Historical!G26</f>
         <v>0.0871606545184083</v>
       </c>
@@ -12296,19 +12278,19 @@
       <c r="A48" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="C48" s="44" t="n">
+      <c r="C48" s="42" t="n">
         <f aca="false">-Historical!D57/Historical!D8*365</f>
         <v>25.7946040034813</v>
       </c>
-      <c r="D48" s="44" t="n">
+      <c r="D48" s="42" t="n">
         <f aca="false">-Historical!E57/Historical!E8*365</f>
         <v>25.0696692470091</v>
       </c>
-      <c r="E48" s="44" t="n">
+      <c r="E48" s="42" t="n">
         <f aca="false">-Historical!F57/Historical!F8*365</f>
         <v>26.1390762843799</v>
       </c>
-      <c r="F48" s="44" t="n">
+      <c r="F48" s="42" t="n">
         <f aca="false">-Historical!G57/Historical!G8*365</f>
         <v>24.5211675310578</v>
       </c>
@@ -12317,19 +12299,19 @@
       <c r="A49" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="C49" s="44" t="n">
+      <c r="C49" s="42" t="n">
         <f aca="false">Historical!D58/Historical!D7*365</f>
         <v>12.1119777895294</v>
       </c>
-      <c r="D49" s="44" t="n">
+      <c r="D49" s="42" t="n">
         <f aca="false">Historical!E58/Historical!E7*365</f>
         <v>10.8515694076039</v>
       </c>
-      <c r="E49" s="44" t="n">
+      <c r="E49" s="42" t="n">
         <f aca="false">Historical!F58/Historical!F7*365</f>
         <v>11.3065925337569</v>
       </c>
-      <c r="F49" s="44" t="n">
+      <c r="F49" s="42" t="n">
         <f aca="false">Historical!G58/Historical!G7*365</f>
         <v>11.7752882112309</v>
       </c>
@@ -12338,19 +12320,19 @@
       <c r="A50" s="23" t="s">
         <v>369</v>
       </c>
-      <c r="C50" s="44" t="n">
+      <c r="C50" s="42" t="n">
         <f aca="false">-Historical!D64/Historical!D7*365</f>
         <v>46.2523135906928</v>
       </c>
-      <c r="D50" s="44" t="n">
+      <c r="D50" s="42" t="n">
         <f aca="false">-Historical!E64/Historical!E7*365</f>
         <v>42.5792992926614</v>
       </c>
-      <c r="E50" s="44" t="n">
+      <c r="E50" s="42" t="n">
         <f aca="false">-Historical!F64/Historical!F7*365</f>
         <v>44.1935563939635</v>
       </c>
-      <c r="F50" s="44" t="n">
+      <c r="F50" s="42" t="n">
         <f aca="false">-Historical!G64/Historical!G7*365</f>
         <v>46.2867236891038</v>
       </c>
@@ -12359,19 +12341,19 @@
       <c r="A51" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="C51" s="39" t="n">
+      <c r="C51" s="37" t="n">
         <f aca="false">Historical!D123/Historical!C53</f>
         <v>0.16870273414776</v>
       </c>
-      <c r="D51" s="39" t="n">
+      <c r="D51" s="37" t="n">
         <f aca="false">Historical!E123/Historical!D53</f>
         <v>0.170769230769231</v>
       </c>
-      <c r="E51" s="39" t="n">
+      <c r="E51" s="37" t="n">
         <f aca="false">Historical!F123/Historical!E53</f>
         <v>0.150107779737409</v>
       </c>
-      <c r="F51" s="39" t="n">
+      <c r="F51" s="37" t="n">
         <f aca="false">Historical!G123/Historical!F53</f>
         <v>0.136452534978186</v>
       </c>
@@ -12380,19 +12362,19 @@
       <c r="A52" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="C52" s="44" t="n">
+      <c r="C52" s="42" t="n">
         <f aca="false">-Historical!D117</f>
         <v>103.3</v>
       </c>
-      <c r="D52" s="44" t="n">
+      <c r="D52" s="42" t="n">
         <f aca="false">-Historical!E117</f>
         <v>198.1</v>
       </c>
-      <c r="E52" s="44" t="n">
+      <c r="E52" s="42" t="n">
         <f aca="false">-Historical!F117</f>
         <v>240.9</v>
       </c>
-      <c r="F52" s="44" t="n">
+      <c r="F52" s="42" t="n">
         <f aca="false">-Historical!G117</f>
         <v>285.4</v>
       </c>
@@ -12439,7 +12421,7 @@
       <c r="A57" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="C57" s="33" t="n">
+      <c r="C57" s="31" t="n">
         <v>0.021</v>
       </c>
       <c r="L57" s="16" t="s">
@@ -12461,7 +12443,7 @@
       <c r="A59" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="C59" s="52" t="s">
+      <c r="C59" s="50" t="s">
         <v>413</v>
       </c>
       <c r="L59" s="16" t="s">
@@ -12483,7 +12465,7 @@
       <c r="A61" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="C61" s="33" t="n">
+      <c r="C61" s="31" t="n">
         <v>0.02</v>
       </c>
       <c r="L61" s="16" t="s">
@@ -12536,10 +12518,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="B4" s="53" t="n">
+      <c r="B4" s="51" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="23" t="str">
@@ -12548,22 +12530,22 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="34" t="s">
         <v>422</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="34" t="s">
         <v>424</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="34" t="s">
         <v>425</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="34" t="s">
         <v>426</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="34" t="s">
         <v>427</v>
       </c>
     </row>
@@ -12571,9 +12553,9 @@
       <c r="A7" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="27" t="n">
         <f aca="false">INDEX(B7:D7,1,$B$4)</f>
         <v>0</v>
@@ -12583,9 +12565,9 @@
       <c r="A8" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="30" t="n">
         <f aca="false">INDEX(B8:D8,1,$B$4)</f>
         <v>0</v>
@@ -12595,9 +12577,9 @@
       <c r="A9" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="27" t="n">
         <f aca="false">INDEX(B9:D9,1,$B$4)</f>
         <v>0</v>
@@ -12607,9 +12589,9 @@
       <c r="A10" s="23" t="s">
         <v>429</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="27" t="n">
         <f aca="false">INDEX(B10:D10,1,$B$4)</f>
         <v>0</v>
@@ -12650,27 +12632,27 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>434</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="34" t="s">
         <v>436</v>
       </c>
     </row>
@@ -12678,8 +12660,8 @@
       <c r="A6" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="44" t="n">
+      <c r="B6" s="53"/>
+      <c r="C6" s="42" t="n">
         <f aca="false">Historical!G36</f>
         <v>1897.2</v>
       </c>
@@ -12696,8 +12678,8 @@
       <c r="A7" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="44" t="n">
+      <c r="B7" s="53"/>
+      <c r="C7" s="42" t="n">
         <f aca="false">Historical!G37</f>
         <v>254</v>
       </c>
@@ -12714,8 +12696,8 @@
       <c r="A8" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="44" t="n">
+      <c r="B8" s="53"/>
+      <c r="C8" s="42" t="n">
         <f aca="false">Historical!G7</f>
         <v>2151.2</v>
       </c>
@@ -12732,8 +12714,8 @@
       <c r="A9" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="44" t="n">
+      <c r="B9" s="53"/>
+      <c r="C9" s="42" t="n">
         <f aca="false">Historical!G24</f>
         <v>187.5</v>
       </c>
@@ -12750,8 +12732,8 @@
       <c r="A10" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="44" t="n">
+      <c r="B10" s="53"/>
+      <c r="C10" s="42" t="n">
         <f aca="false">Historical!G25</f>
         <v>171.9</v>
       </c>
@@ -12768,8 +12750,8 @@
       <c r="A11" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="44" t="n">
+      <c r="B11" s="53"/>
+      <c r="C11" s="42" t="n">
         <f aca="false">Historical!G97</f>
         <v>337</v>
       </c>
@@ -12786,8 +12768,8 @@
       <c r="A12" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="44" t="n">
+      <c r="B12" s="53"/>
+      <c r="C12" s="42" t="n">
         <f aca="false">Historical!G117</f>
         <v>-285.4</v>
       </c>
@@ -12804,8 +12786,8 @@
       <c r="A13" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="44" t="n">
+      <c r="B13" s="53"/>
+      <c r="C13" s="42" t="n">
         <f aca="false">Historical!G61</f>
         <v>70.8</v>
       </c>
@@ -12819,25 +12801,25 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="43" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="34" t="s">
         <v>442</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="34" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12845,8 +12827,8 @@
       <c r="A18" s="23" t="s">
         <v>444</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="23" t="str">
         <f aca="false">IF(OR(B18="",C18=""),"",C18-B18)</f>
         <v/>
@@ -12856,8 +12838,8 @@
       <c r="A19" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="23" t="str">
         <f aca="false">IF(OR(B19="",C19=""),"",C19-B19)</f>
         <v/>
@@ -12867,8 +12849,8 @@
       <c r="A20" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="23" t="str">
         <f aca="false">IF(OR(B20="",C20=""),"",C20-B20)</f>
         <v/>
@@ -12878,8 +12860,8 @@
       <c r="A21" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="23" t="str">
         <f aca="false">IF(OR(B21="",C21=""),"",C21-B21)</f>
         <v/>
@@ -12960,23 +12942,23 @@
       <c r="B6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="42" t="n">
         <f aca="false">Historical!C16</f>
         <v>145.6</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="42" t="n">
         <f aca="false">Historical!D16</f>
         <v>148.3</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="42" t="n">
         <f aca="false">Historical!E16</f>
         <v>188.3</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="42" t="n">
         <f aca="false">Historical!F16</f>
         <v>203.9</v>
       </c>
-      <c r="G6" s="44" t="n">
+      <c r="G6" s="42" t="n">
         <f aca="false">Historical!G16</f>
         <v>167.4</v>
       </c>
@@ -12988,19 +12970,19 @@
       <c r="B7" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="31" t="n">
         <v>0.19</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="31" t="n">
         <v>0.19</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="31" t="n">
         <v>0.235</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="31" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -13039,51 +13021,51 @@
       <c r="B9" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
         <v>458</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
         <v>459</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
         <v>460</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
@@ -13120,23 +13102,23 @@
       <c r="B15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="42" t="n">
         <f aca="false">Historical!C17</f>
         <v>-28.1</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="42" t="n">
         <f aca="false">Historical!D17</f>
         <v>-28</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="42" t="n">
         <f aca="false">Historical!E17</f>
         <v>-45.8</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="42" t="n">
         <f aca="false">Historical!F17</f>
         <v>-50.5</v>
       </c>
-      <c r="G15" s="44" t="n">
+      <c r="G15" s="42" t="n">
         <f aca="false">Historical!G17</f>
         <v>-45.2</v>
       </c>
@@ -13266,11 +13248,11 @@
       <c r="B22" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
@@ -13279,11 +13261,11 @@
       <c r="B23" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
@@ -13348,23 +13330,23 @@
       <c r="B26" s="16" t="s">
         <v>473</v>
       </c>
-      <c r="C26" s="44" t="n">
+      <c r="C26" s="42" t="n">
         <f aca="false">Historical!C93</f>
         <v>-19.2</v>
       </c>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="42" t="n">
         <f aca="false">Historical!D93</f>
         <v>-13.3</v>
       </c>
-      <c r="E26" s="44" t="n">
+      <c r="E26" s="42" t="n">
         <f aca="false">Historical!E93</f>
         <v>-11.9</v>
       </c>
-      <c r="F26" s="44" t="n">
+      <c r="F26" s="42" t="n">
         <f aca="false">Historical!F93</f>
         <v>-27.7</v>
       </c>
-      <c r="G26" s="44" t="n">
+      <c r="G26" s="42" t="n">
         <f aca="false">Historical!G93</f>
         <v>-31.5</v>
       </c>
@@ -13410,7 +13392,7 @@
       <c r="B30" s="16" t="s">
         <v>476</v>
       </c>
-      <c r="C30" s="56"/>
+      <c r="C30" s="55"/>
       <c r="D30" s="28" t="n">
         <f aca="false">C34</f>
         <v>0</v>
@@ -13435,11 +13417,11 @@
       <c r="B31" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
@@ -13448,11 +13430,11 @@
       <c r="B32" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
@@ -13461,11 +13443,11 @@
       <c r="B33" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
@@ -13502,23 +13484,23 @@
       <c r="B35" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="44" t="n">
+      <c r="C35" s="42" t="n">
         <f aca="false">-Historical!C72</f>
         <v>10</v>
       </c>
-      <c r="D35" s="44" t="n">
+      <c r="D35" s="42" t="n">
         <f aca="false">-Historical!D72</f>
         <v>26.3</v>
       </c>
-      <c r="E35" s="44" t="n">
+      <c r="E35" s="42" t="n">
         <f aca="false">-Historical!E72</f>
         <v>54.7</v>
       </c>
-      <c r="F35" s="44" t="n">
+      <c r="F35" s="42" t="n">
         <f aca="false">-Historical!F72</f>
         <v>72.6</v>
       </c>
-      <c r="G35" s="44" t="n">
+      <c r="G35" s="42" t="n">
         <f aca="false">-Historical!G72</f>
         <v>93.7</v>
       </c>
@@ -13558,23 +13540,23 @@
       <c r="B38" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="44" t="n">
+      <c r="C38" s="42" t="n">
         <f aca="false">-Historical!C117</f>
         <v>54.3</v>
       </c>
-      <c r="D38" s="44" t="n">
+      <c r="D38" s="42" t="n">
         <f aca="false">-Historical!D117</f>
         <v>103.3</v>
       </c>
-      <c r="E38" s="44" t="n">
+      <c r="E38" s="42" t="n">
         <f aca="false">-Historical!E117</f>
         <v>198.1</v>
       </c>
-      <c r="F38" s="44" t="n">
+      <c r="F38" s="42" t="n">
         <f aca="false">-Historical!F117</f>
         <v>240.9</v>
       </c>
-      <c r="G38" s="44" t="n">
+      <c r="G38" s="42" t="n">
         <f aca="false">-Historical!G117</f>
         <v>285.4</v>
       </c>
@@ -13586,23 +13568,23 @@
       <c r="B39" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="44" t="n">
+      <c r="C39" s="42" t="n">
         <f aca="false">Historical!C123+Historical!C122</f>
         <v>58.7</v>
       </c>
-      <c r="D39" s="44" t="n">
+      <c r="D39" s="42" t="n">
         <f aca="false">Historical!D123+Historical!D122</f>
         <v>62.7</v>
       </c>
-      <c r="E39" s="44" t="n">
+      <c r="E39" s="42" t="n">
         <f aca="false">Historical!E123+Historical!E122</f>
         <v>70.5</v>
       </c>
-      <c r="F39" s="44" t="n">
+      <c r="F39" s="42" t="n">
         <f aca="false">Historical!F123+Historical!F122</f>
         <v>80.8</v>
       </c>
-      <c r="G39" s="44" t="n">
+      <c r="G39" s="42" t="n">
         <f aca="false">Historical!G123+Historical!G122</f>
         <v>95.4</v>
       </c>
@@ -13647,64 +13629,64 @@
       <c r="G43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="34" t="s">
         <v>488</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="56" t="s">
         <v>489</v>
       </c>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
     </row>
     <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="16" t="s">
@@ -13726,34 +13708,34 @@
       <c r="A53" s="23" t="s">
         <v>492</v>
       </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="60"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="B54" s="60"/>
-      <c r="C54" s="60"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="60"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="60"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="s">
         <v>494</v>
       </c>
-      <c r="B55" s="60"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="s">
@@ -13807,34 +13789,34 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="34" t="s">
         <v>498</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="34" t="s">
         <v>239</v>
       </c>
     </row>
@@ -13845,23 +13827,23 @@
       <c r="B5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="61" t="n">
+      <c r="C5" s="60" t="n">
         <f aca="false">ROUND(Historical!C13-Historical!C30,1)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="61" t="n">
+      <c r="D5" s="60" t="n">
         <f aca="false">ROUND(Historical!D13-Historical!D30,1)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="61" t="n">
+      <c r="E5" s="60" t="n">
         <f aca="false">ROUND(Historical!E13-Historical!E30,1)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="61" t="n">
+      <c r="F5" s="60" t="n">
         <f aca="false">ROUND(Historical!F13-Historical!F30,1)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="61" t="n">
+      <c r="G5" s="60" t="n">
         <f aca="false">ROUND(Historical!G13-Historical!G30,1)</f>
         <v>0</v>
       </c>
@@ -13873,23 +13855,23 @@
       <c r="B6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="61" t="n">
+      <c r="C6" s="60" t="n">
         <f aca="false">ROUND(Historical!C16-Historical!C31,1)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="61" t="n">
+      <c r="D6" s="60" t="n">
         <f aca="false">ROUND(Historical!D16-Historical!D31,1)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="61" t="n">
+      <c r="E6" s="60" t="n">
         <f aca="false">ROUND(Historical!E16-Historical!E31,1)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="61" t="n">
+      <c r="F6" s="60" t="n">
         <f aca="false">ROUND(Historical!F16-Historical!F31,1)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="61" t="n">
+      <c r="G6" s="60" t="n">
         <f aca="false">ROUND(Historical!G16-Historical!G31,1)</f>
         <v>0</v>
       </c>
@@ -13901,23 +13883,23 @@
       <c r="B7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="60" t="n">
         <f aca="false">ROUND(Historical!C18-Historical!C32,1)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="61" t="n">
+      <c r="D7" s="60" t="n">
         <f aca="false">ROUND(Historical!D18-Historical!D32,1)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="61" t="n">
+      <c r="E7" s="60" t="n">
         <f aca="false">ROUND(Historical!E18-Historical!E32,1)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="61" t="n">
+      <c r="F7" s="60" t="n">
         <f aca="false">ROUND(Historical!F18-Historical!F32,1)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="61" t="n">
+      <c r="G7" s="60" t="n">
         <f aca="false">ROUND(Historical!G18-Historical!G32,1)</f>
         <v>0</v>
       </c>
@@ -13929,23 +13911,23 @@
       <c r="B8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="61" t="n">
+      <c r="C8" s="60" t="n">
         <f aca="false">ROUND(Historical!C25-Historical!C33,1)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="61" t="n">
+      <c r="D8" s="60" t="n">
         <f aca="false">ROUND(Historical!D25-Historical!D33,1)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="61" t="n">
+      <c r="E8" s="60" t="n">
         <f aca="false">ROUND(Historical!E25-Historical!E33,1)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="61" t="n">
+      <c r="F8" s="60" t="n">
         <f aca="false">ROUND(Historical!F25-Historical!F33,1)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="61" t="n">
+      <c r="G8" s="60" t="n">
         <f aca="false">ROUND(Historical!G25-Historical!G33,1)</f>
         <v>0</v>
       </c>
@@ -13957,23 +13939,23 @@
       <c r="B9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="61" t="n">
+      <c r="C9" s="60" t="n">
         <f aca="false">ROUND(Historical!C36+Historical!C37-Historical!C7,1)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="61" t="n">
+      <c r="D9" s="60" t="n">
         <f aca="false">ROUND(Historical!D36+Historical!D37-Historical!D7,1)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="61" t="n">
+      <c r="E9" s="60" t="n">
         <f aca="false">ROUND(Historical!E36+Historical!E37-Historical!E7,1)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="61" t="n">
+      <c r="F9" s="60" t="n">
         <f aca="false">ROUND(Historical!F36+Historical!F37-Historical!F7,1)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="61" t="n">
+      <c r="G9" s="60" t="n">
         <f aca="false">ROUND(Historical!G36+Historical!G37-Historical!G7,1)</f>
         <v>0</v>
       </c>
@@ -13985,23 +13967,23 @@
       <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="61" t="n">
+      <c r="C10" s="60" t="n">
         <f aca="false">ROUND(Historical!C63-Historical!C83,1)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="60" t="n">
         <f aca="false">ROUND(Historical!D63-Historical!D83,1)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="E10" s="60" t="n">
         <f aca="false">ROUND(Historical!E63-Historical!E83,1)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="61" t="n">
+      <c r="F10" s="60" t="n">
         <f aca="false">ROUND(Historical!F63-Historical!F83,1)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="60" t="n">
         <f aca="false">ROUND(Historical!G63-Historical!G83,1)</f>
         <v>0</v>
       </c>
@@ -14013,23 +13995,23 @@
       <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="61" t="n">
+      <c r="C11" s="60" t="n">
         <f aca="false">ROUND(Historical!C77-Historical!C84,1)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="61" t="n">
+      <c r="D11" s="60" t="n">
         <f aca="false">ROUND(Historical!D77-Historical!D84,1)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="61" t="n">
+      <c r="E11" s="60" t="n">
         <f aca="false">ROUND(Historical!E77-Historical!E84,1)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="61" t="n">
+      <c r="F11" s="60" t="n">
         <f aca="false">ROUND(Historical!F77-Historical!F84,1)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="61" t="n">
+      <c r="G11" s="60" t="n">
         <f aca="false">ROUND(Historical!G77-Historical!G84,1)</f>
         <v>0</v>
       </c>
@@ -14041,35 +14023,35 @@
       <c r="B12" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="C12" s="61" t="n">
+      <c r="C12" s="60" t="n">
         <f aca="false">ROUND(Historical!C77-Historical!C82,1)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="60" t="n">
         <f aca="false">ROUND(Historical!D77-Historical!D82,1)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="61" t="n">
+      <c r="E12" s="60" t="n">
         <f aca="false">ROUND(Historical!E77-Historical!E82,1)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="61" t="n">
+      <c r="F12" s="60" t="n">
         <f aca="false">ROUND(Historical!F77-Historical!F82,1)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="61" t="n">
+      <c r="G12" s="60" t="n">
         <f aca="false">ROUND(Historical!G77-Historical!G82,1)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="60" t="n">
         <f aca="false">ROUND(Forecast!H77-Forecast!H82,1)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="61" t="n">
+      <c r="I12" s="60" t="n">
         <f aca="false">ROUND(Forecast!I77-Forecast!I82,1)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="61" t="n">
+      <c r="J12" s="60" t="n">
         <f aca="false">ROUND(Forecast!J77-Forecast!J82,1)</f>
         <v>0</v>
       </c>
@@ -14081,35 +14063,35 @@
       <c r="B13" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="C13" s="61" t="n">
+      <c r="C13" s="60" t="n">
         <f aca="false">ROUND(Historical!C113-Historical!C61,1)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="60" t="n">
         <f aca="false">ROUND(Historical!D113-Historical!D61,1)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="60" t="n">
         <f aca="false">ROUND(Historical!E113-Historical!E61,1)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="61" t="n">
+      <c r="F13" s="60" t="n">
         <f aca="false">ROUND(Historical!F113-Historical!F61,1)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="n">
+      <c r="G13" s="60" t="n">
         <f aca="false">ROUND(Historical!G113-Historical!G61,1)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="60" t="n">
         <f aca="false">ROUND(Forecast!H113-Forecast!H61,1)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="61" t="n">
+      <c r="I13" s="60" t="n">
         <f aca="false">ROUND(Forecast!I113-Forecast!I61,1)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="61" t="n">
+      <c r="J13" s="60" t="n">
         <f aca="false">ROUND(Forecast!J113-Forecast!J61,1)</f>
         <v>0</v>
       </c>
@@ -14121,23 +14103,23 @@
       <c r="B14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="61" t="n">
+      <c r="C14" s="60" t="n">
         <f aca="false">ROUND(Historical!C111-Historical!C114,1)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="61" t="n">
+      <c r="D14" s="60" t="n">
         <f aca="false">ROUND(Historical!D111-Historical!D114,1)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="61" t="n">
+      <c r="E14" s="60" t="n">
         <f aca="false">ROUND(Historical!E111-Historical!E114,1)</f>
         <v>-0</v>
       </c>
-      <c r="F14" s="61" t="n">
+      <c r="F14" s="60" t="n">
         <f aca="false">ROUND(Historical!F111-Historical!F114,1)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="61" t="n">
+      <c r="G14" s="60" t="n">
         <f aca="false">ROUND(Historical!G111-Historical!G114,1)</f>
         <v>0</v>
       </c>
@@ -14149,23 +14131,23 @@
       <c r="B15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="61" t="n">
+      <c r="C15" s="60" t="n">
         <f aca="false">ROUND(Historical!C138-Historical!C92,1)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="61" t="n">
+      <c r="D15" s="60" t="n">
         <f aca="false">ROUND(Historical!D138-Historical!D92,1)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="61" t="n">
+      <c r="E15" s="60" t="n">
         <f aca="false">ROUND(Historical!E138-Historical!E92,1)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="61" t="n">
+      <c r="F15" s="60" t="n">
         <f aca="false">ROUND(Historical!F138-Historical!F92,1)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="61" t="n">
+      <c r="G15" s="60" t="n">
         <f aca="false">ROUND(Historical!G138-Historical!G92,1)</f>
         <v>0</v>
       </c>
@@ -14177,23 +14159,23 @@
       <c r="B16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="61" t="n">
+      <c r="C16" s="60" t="n">
         <f aca="false">ROUND(Historical!C121-Historical!C18,1)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="61" t="n">
+      <c r="D16" s="60" t="n">
         <f aca="false">ROUND(Historical!D121-Historical!D18,1)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="61" t="n">
+      <c r="E16" s="60" t="n">
         <f aca="false">ROUND(Historical!E121-Historical!E18,1)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="61" t="n">
+      <c r="F16" s="60" t="n">
         <f aca="false">ROUND(Historical!F121-Historical!F18,1)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="61" t="n">
+      <c r="G16" s="60" t="n">
         <f aca="false">ROUND(Historical!G121-Historical!G18,1)</f>
         <v>0</v>
       </c>
@@ -14205,38 +14187,38 @@
       <c r="B17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="61" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">ROUND(Historical!C46,1)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="61" t="n">
+      <c r="D17" s="60" t="n">
         <f aca="false">ROUND(Historical!D46,1)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="61" t="n">
+      <c r="E17" s="60" t="n">
         <f aca="false">ROUND(Historical!E46,1)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="61" t="n">
+      <c r="F17" s="60" t="n">
         <f aca="false">ROUND(Historical!F46,1)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="61" t="n">
+      <c r="G17" s="60" t="n">
         <f aca="false">ROUND(Historical!G46,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="43" t="s">
         <v>514</v>
       </c>
-      <c r="C19" s="62" t="n">
+      <c r="C19" s="61" t="n">
         <f aca="false">SUMPRODUCT(ABS(C5:G17))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="43" t="s">
         <v>515</v>
       </c>
       <c r="C20" s="25" t="str">
@@ -14245,7 +14227,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="43" t="s">
         <v>516</v>
       </c>
     </row>
@@ -14256,23 +14238,23 @@
       <c r="B23" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="61" t="str">
+      <c r="C23" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C9:C13)=0,"",ROUND('Tax &amp; Audit'!C16,1))</f>
         <v/>
       </c>
-      <c r="D23" s="61" t="str">
+      <c r="D23" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D9:D13)=0,"",ROUND('Tax &amp; Audit'!D16,1))</f>
         <v/>
       </c>
-      <c r="E23" s="61" t="str">
+      <c r="E23" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E9:E13)=0,"",ROUND('Tax &amp; Audit'!E16,1))</f>
         <v/>
       </c>
-      <c r="F23" s="61" t="str">
+      <c r="F23" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F9:F13)=0,"",ROUND('Tax &amp; Audit'!F16,1))</f>
         <v/>
       </c>
-      <c r="G23" s="61" t="str">
+      <c r="G23" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G9:G13)=0,"",ROUND('Tax &amp; Audit'!G16,1))</f>
         <v/>
       </c>
@@ -14284,23 +14266,23 @@
       <c r="B24" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="61" t="str">
+      <c r="C24" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C22:C23)=0,"",ROUND('Tax &amp; Audit'!C25,1))</f>
         <v/>
       </c>
-      <c r="D24" s="61" t="str">
+      <c r="D24" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D22:D23)=0,"",ROUND('Tax &amp; Audit'!D25,1))</f>
         <v/>
       </c>
-      <c r="E24" s="61" t="str">
+      <c r="E24" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E22:E23)=0,"",ROUND('Tax &amp; Audit'!E25,1))</f>
         <v/>
       </c>
-      <c r="F24" s="61" t="str">
+      <c r="F24" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F22:F23)=0,"",ROUND('Tax &amp; Audit'!F25,1))</f>
         <v/>
       </c>
-      <c r="G24" s="61" t="str">
+      <c r="G24" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G22:G23)=0,"",ROUND('Tax &amp; Audit'!G25,1))</f>
         <v/>
       </c>
@@ -14312,43 +14294,43 @@
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="61" t="str">
+      <c r="C25" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C31:C33)=0,"",ROUND('Tax &amp; Audit'!C36,1))</f>
         <v/>
       </c>
-      <c r="D25" s="61" t="str">
+      <c r="D25" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D31:D33)=0,"",ROUND('Tax &amp; Audit'!D36,1))</f>
         <v/>
       </c>
-      <c r="E25" s="61" t="str">
+      <c r="E25" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E31:E33)=0,"",ROUND('Tax &amp; Audit'!E36,1))</f>
         <v/>
       </c>
-      <c r="F25" s="61" t="str">
+      <c r="F25" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F31:F33)=0,"",ROUND('Tax &amp; Audit'!F36,1))</f>
         <v/>
       </c>
-      <c r="G25" s="61" t="str">
+      <c r="G25" s="60" t="str">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G31:G33)=0,"",ROUND('Tax &amp; Audit'!G36,1))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="43" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="34" t="s">
         <v>521</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="34" t="s">
         <v>522</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="34" t="s">
         <v>523</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="34" t="s">
         <v>524</v>
       </c>
     </row>
@@ -14356,37 +14338,37 @@
       <c r="A30" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="55"/>
+      <c r="B30" s="54"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="B31" s="55"/>
+      <c r="B31" s="54"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
         <v>527</v>
       </c>
-      <c r="B32" s="55"/>
+      <c r="B32" s="54"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
         <v>528</v>
       </c>
-      <c r="B33" s="55"/>
+      <c r="B33" s="54"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
         <v>529</v>
       </c>
-      <c r="B34" s="55"/>
+      <c r="B34" s="54"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
         <v>530</v>
       </c>
-      <c r="B35" s="55"/>
+      <c r="B35" s="54"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:J17">

--- a/model/GRG_model_v0.3.xlsx
+++ b/model/GRG_model_v0.3.xlsx
@@ -1323,7 +1323,7 @@
     <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t xml:space="preserve">Rising: 55%, 57%, 60% (FY22–FY24)</t>
+    <t xml:space="preserve">Rising: 55%, 57%, 60%, 66% (FY22–FY25); revised 11 Oct after FY25 actuals</t>
   </si>
   <si>
     <t xml:space="preserve">Company-managed like-for-like growth</t>
@@ -7027,11 +7027,11 @@
       </c>
       <c r="I15" s="28" t="n">
         <f aca="false">-I150-I151</f>
-        <v>-19.3093542349088</v>
+        <v>-19.3352119466542</v>
       </c>
       <c r="J15" s="28" t="n">
         <f aca="false">-J150-J151</f>
-        <v>-19.851134861956</v>
+        <v>-19.9040816050538</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7064,11 +7064,11 @@
       </c>
       <c r="I16" s="44" t="n">
         <f aca="false">I13+I14+I15</f>
-        <v>-29.3093542349088</v>
+        <v>-29.3352119466542</v>
       </c>
       <c r="J16" s="44" t="n">
         <f aca="false">J13+J14+J15</f>
-        <v>-24.851134861956</v>
+        <v>-24.9040816050538</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7104,11 +7104,11 @@
       </c>
       <c r="I17" s="28" t="n">
         <f aca="false">-Drivers!$D$18*I16</f>
-        <v>7.62043210107628</v>
+        <v>7.62715510613009</v>
       </c>
       <c r="J17" s="28" t="n">
         <f aca="false">-Drivers!$E$18*J16</f>
-        <v>6.46129506410856</v>
+        <v>6.47506121731399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="I18" s="44" t="n">
         <f aca="false">I16+I17</f>
-        <v>-21.6889221338325</v>
+        <v>-21.7080568405241</v>
       </c>
       <c r="J18" s="44" t="n">
         <f aca="false">J16+J17</f>
-        <v>-18.3898397978475</v>
+        <v>-18.4290203877398</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7346,11 +7346,11 @@
       </c>
       <c r="I25" s="44" t="n">
         <f aca="false">I16-I21-I22</f>
-        <v>-19.3093542349088</v>
+        <v>-19.3352119466542</v>
       </c>
       <c r="J25" s="44" t="n">
         <f aca="false">J16-J21-J22</f>
-        <v>-19.851134861956</v>
+        <v>-19.9040816050538</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7787,15 +7787,15 @@
       </c>
       <c r="H41" s="30" t="n">
         <f aca="false">G41+(1-Drivers!$C$7)*Drivers!$C$6</f>
-        <v>644</v>
+        <v>640.85</v>
       </c>
       <c r="I41" s="30" t="n">
         <f aca="false">H41+(1-Drivers!$D$7)*Drivers!$D$6</f>
-        <v>688</v>
+        <v>681.55</v>
       </c>
       <c r="J41" s="30" t="n">
         <f aca="false">I41+(1-Drivers!$E$7)*Drivers!$E$6</f>
-        <v>732</v>
+        <v>722.25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7824,15 +7824,15 @@
       </c>
       <c r="H42" s="30" t="n">
         <f aca="false">IF(H41="","",H40-H41)</f>
-        <v>2200</v>
+        <v>2203.15</v>
       </c>
       <c r="I42" s="30" t="n">
         <f aca="false">IF(I41="","",I40-I41)</f>
-        <v>2266</v>
+        <v>2272.45</v>
       </c>
       <c r="J42" s="30" t="n">
         <f aca="false">IF(J41="","",J40-J41)</f>
-        <v>2332</v>
+        <v>2341.75</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8187,15 +8187,15 @@
       </c>
       <c r="H54" s="28" t="n">
         <f aca="false">G54*H42/G42</f>
-        <v>425.175479644361</v>
+        <v>425.784253626579</v>
       </c>
       <c r="I54" s="28" t="n">
         <f aca="false">H54*I42/H42</f>
-        <v>437.930744033692</v>
+        <v>439.177281235377</v>
       </c>
       <c r="J54" s="28" t="n">
         <f aca="false">I54*J42/I42</f>
-        <v>450.686008423023</v>
+        <v>452.570308844174</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8261,15 +8261,15 @@
       </c>
       <c r="H56" s="44" t="n">
         <f aca="false">SUM(H52:H55)</f>
-        <v>1360.20197964436</v>
+        <v>1360.81075362658</v>
       </c>
       <c r="I56" s="44" t="n">
         <f aca="false">SUM(I52:I55)</f>
-        <v>1409.49396653369</v>
+        <v>1410.74050373538</v>
       </c>
       <c r="J56" s="44" t="n">
         <f aca="false">SUM(J52:J55)</f>
-        <v>1448.66174188552</v>
+        <v>1450.54604230667</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8455,15 +8455,15 @@
       </c>
       <c r="H61" s="28" t="n">
         <f aca="false">H113</f>
-        <v>-210.095167646701</v>
+        <v>-210.040923379036</v>
       </c>
       <c r="I61" s="28" t="n">
         <f aca="false">I113</f>
-        <v>-359.882446244934</v>
+        <v>-359.790509355931</v>
       </c>
       <c r="J61" s="28" t="n">
         <f aca="false">J113</f>
-        <v>-483.794438638808</v>
+        <v>-483.684855011667</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8492,15 +8492,15 @@
       </c>
       <c r="H62" s="44" t="n">
         <f aca="false">SUM(H57:H61)</f>
-        <v>-210.095167646701</v>
+        <v>-210.040923379036</v>
       </c>
       <c r="I62" s="44" t="n">
         <f aca="false">SUM(I57:I61)</f>
-        <v>-359.882446244934</v>
+        <v>-359.790509355931</v>
       </c>
       <c r="J62" s="44" t="n">
         <f aca="false">SUM(J57:J61)</f>
-        <v>-483.794438638808</v>
+        <v>-483.684855011667</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8529,15 +8529,15 @@
       </c>
       <c r="H63" s="44" t="n">
         <f aca="false">H56+H62</f>
-        <v>1150.10681199766</v>
+        <v>1150.76983024754</v>
       </c>
       <c r="I63" s="44" t="n">
         <f aca="false">I56+I62</f>
-        <v>1049.61152028876</v>
+        <v>1050.94999437945</v>
       </c>
       <c r="J63" s="44" t="n">
         <f aca="false">J56+J62</f>
-        <v>964.867303246715</v>
+        <v>966.861187295007</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8646,15 +8646,15 @@
       </c>
       <c r="H66" s="28" t="n">
         <f aca="false">-H146*Drivers!$C$35</f>
-        <v>-64.3653907346748</v>
+        <v>-64.4575502714085</v>
       </c>
       <c r="I66" s="28" t="n">
         <f aca="false">-I146*Drivers!$D$35</f>
-        <v>-66.296352456715</v>
+        <v>-66.4850600795508</v>
       </c>
       <c r="J66" s="28" t="n">
         <f aca="false">-J146*Drivers!$E$35</f>
-        <v>-68.2273141787553</v>
+        <v>-68.512569887693</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8720,15 +8720,15 @@
       </c>
       <c r="H68" s="44" t="n">
         <f aca="false">SUM(H64:H67)</f>
-        <v>-111.765390734675</v>
+        <v>-111.857550271409</v>
       </c>
       <c r="I68" s="44" t="n">
         <f aca="false">SUM(I64:I67)</f>
-        <v>-88.696352456715</v>
+        <v>-88.8850600795508</v>
       </c>
       <c r="J68" s="44" t="n">
         <f aca="false">SUM(J64:J67)</f>
-        <v>-80.6273141787553</v>
+        <v>-80.912569887693</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8834,15 +8834,15 @@
       </c>
       <c r="H71" s="28" t="n">
         <f aca="false">-H146*(1-Drivers!$C$35)</f>
-        <v>-398.694974262985</v>
+        <v>-399.265832976135</v>
       </c>
       <c r="I71" s="28" t="n">
         <f aca="false">-I146*(1-Drivers!$D$35)</f>
-        <v>-410.655823490875</v>
+        <v>-411.824724665419</v>
       </c>
       <c r="J71" s="28" t="n">
         <f aca="false">-J146*(1-Drivers!$E$35)</f>
-        <v>-422.616672718765</v>
+        <v>-424.383616354703</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8982,15 +8982,15 @@
       </c>
       <c r="H75" s="44" t="n">
         <f aca="false">SUM(H69:H74)</f>
-        <v>-529.086889262985</v>
+        <v>-529.657747976135</v>
       </c>
       <c r="I75" s="44" t="n">
         <f aca="false">SUM(I69:I74)</f>
-        <v>-545.066777965875</v>
+        <v>-546.235679140419</v>
       </c>
       <c r="J75" s="44" t="n">
         <f aca="false">SUM(J69:J74)</f>
-        <v>-559.93300339964</v>
+        <v>-561.699947035578</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9019,15 +9019,15 @@
       </c>
       <c r="H76" s="44" t="n">
         <f aca="false">H68+H75</f>
-        <v>-640.85227999766</v>
+        <v>-641.515298247543</v>
       </c>
       <c r="I76" s="44" t="n">
         <f aca="false">I68+I75</f>
-        <v>-633.76313042259</v>
+        <v>-635.120739219969</v>
       </c>
       <c r="J76" s="44" t="n">
         <f aca="false">J68+J75</f>
-        <v>-640.560317578395</v>
+        <v>-642.612516923271</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9060,11 +9060,11 @@
       </c>
       <c r="I77" s="44" t="n">
         <f aca="false">I63+I76</f>
-        <v>415.848389866168</v>
+        <v>415.829255159476</v>
       </c>
       <c r="J77" s="44" t="n">
         <f aca="false">J63+J76</f>
-        <v>324.30698566832</v>
+        <v>324.248670371736</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="I81" s="28" t="n">
         <f aca="false">H81+I18+I108</f>
-        <v>388.348389866168</v>
+        <v>388.329255159476</v>
       </c>
       <c r="J81" s="28" t="n">
         <f aca="false">I81+J18+J108</f>
-        <v>296.80698566832</v>
+        <v>296.748670371736</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="I82" s="44" t="n">
         <f aca="false">SUM(I78:I81)</f>
-        <v>415.848389866168</v>
+        <v>415.829255159476</v>
       </c>
       <c r="J82" s="44" t="n">
         <f aca="false">SUM(J78:J81)</f>
-        <v>324.30698566832</v>
+        <v>324.248670371736</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9351,15 +9351,15 @@
       </c>
       <c r="H87" s="28" t="n">
         <f aca="false">H61+H69</f>
-        <v>-235.095167646701</v>
+        <v>-235.040923379036</v>
       </c>
       <c r="I87" s="28" t="n">
         <f aca="false">I61+I69</f>
-        <v>-384.882446244934</v>
+        <v>-384.790509355931</v>
       </c>
       <c r="J87" s="28" t="n">
         <f aca="false">J61+J69</f>
-        <v>-508.794438638808</v>
+        <v>-508.684855011667</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9388,15 +9388,15 @@
       </c>
       <c r="H88" s="28" t="n">
         <f aca="false">H66+H71</f>
-        <v>-463.06036499766</v>
+        <v>-463.723383247543</v>
       </c>
       <c r="I88" s="28" t="n">
         <f aca="false">I66+I71</f>
-        <v>-476.95217594759</v>
+        <v>-478.30978474497</v>
       </c>
       <c r="J88" s="28" t="n">
         <f aca="false">J66+J71</f>
-        <v>-490.84398689752</v>
+        <v>-492.896186242396</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,15 +9425,15 @@
       </c>
       <c r="H89" s="28" t="n">
         <f aca="false">H87+H88</f>
-        <v>-698.155532644361</v>
+        <v>-698.764306626579</v>
       </c>
       <c r="I89" s="28" t="n">
         <f aca="false">I87+I88</f>
-        <v>-861.834622192524</v>
+        <v>-863.100294100901</v>
       </c>
       <c r="J89" s="28" t="n">
         <f aca="false">J87+J88</f>
-        <v>-999.638425536328</v>
+        <v>-1001.58104125406</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9480,11 +9480,11 @@
       </c>
       <c r="I92" s="28" t="n">
         <f aca="false">I13+I145+I144+I147-(I57-H57)-(I58-H58)-(I64-H64)-(I67-H67)</f>
-        <v>165.743109039541</v>
+        <v>165.846600616519</v>
       </c>
       <c r="J92" s="28" t="n">
         <f aca="false">J13+J145+J144+J147-(J57-I57)-(J58-I58)-(J64-I64)-(J67-I67)</f>
-        <v>193.035715523228</v>
+        <v>193.247626847514</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9517,11 +9517,11 @@
       </c>
       <c r="I93" s="28" t="n">
         <f aca="false">I17-(I72-H72)</f>
-        <v>11.6394715760763</v>
+        <v>11.6461945811301</v>
       </c>
       <c r="J93" s="28" t="n">
         <f aca="false">J17-(J72-I72)</f>
-        <v>9.36667126998357</v>
+        <v>9.38043742318899</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9591,11 +9591,11 @@
       </c>
       <c r="I95" s="28" t="n">
         <f aca="false">-I150</f>
-        <v>-18.0593542349088</v>
+        <v>-18.0852119466542</v>
       </c>
       <c r="J95" s="28" t="n">
         <f aca="false">-J150</f>
-        <v>-18.601134861956</v>
+        <v>-18.6540816050538</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9668,11 +9668,11 @@
       </c>
       <c r="I97" s="44" t="n">
         <f aca="false">SUM(I92:I96)</f>
-        <v>158.073226380709</v>
+        <v>158.157583250994</v>
       </c>
       <c r="J97" s="44" t="n">
         <f aca="false">SUM(J92:J96)</f>
-        <v>182.551251931255</v>
+        <v>182.723982665649</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10111,15 +10111,15 @@
       </c>
       <c r="H109" s="28" t="n">
         <f aca="false">-H149</f>
-        <v>-69.125114646701</v>
+        <v>-69.070870379036</v>
       </c>
       <c r="I109" s="28" t="n">
         <f aca="false">-I149</f>
-        <v>-71.1432849789424</v>
+        <v>-71.1899492278895</v>
       </c>
       <c r="J109" s="28" t="n">
         <f aca="false">-J149</f>
-        <v>-73.3116799251287</v>
+        <v>-73.4667639213851</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10148,15 +10148,15 @@
       </c>
       <c r="H110" s="44" t="n">
         <f aca="false">SUM(H103:H109)</f>
-        <v>-139.436114646701</v>
+        <v>-139.381870379036</v>
       </c>
       <c r="I110" s="44" t="n">
         <f aca="false">SUM(I103:I109)</f>
-        <v>-142.860504978942</v>
+        <v>-142.907169227889</v>
       </c>
       <c r="J110" s="44" t="n">
         <f aca="false">SUM(J103:J109)</f>
-        <v>-146.463244325129</v>
+        <v>-146.618328321385</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10185,15 +10185,15 @@
       </c>
       <c r="H111" s="44" t="n">
         <f aca="false">H97+H102+H110</f>
-        <v>-280.895167646701</v>
+        <v>-280.840923379036</v>
       </c>
       <c r="I111" s="44" t="n">
         <f aca="false">I97+I102+I110</f>
-        <v>-149.787278598233</v>
+        <v>-149.749585976895</v>
       </c>
       <c r="J111" s="44" t="n">
         <f aca="false">J97+J102+J110</f>
-        <v>-123.911992393873</v>
+        <v>-123.894345655736</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,11 +10226,11 @@
       </c>
       <c r="I112" s="28" t="n">
         <f aca="false">H113</f>
-        <v>-210.095167646701</v>
+        <v>-210.040923379036</v>
       </c>
       <c r="J112" s="28" t="n">
         <f aca="false">I113</f>
-        <v>-359.882446244934</v>
+        <v>-359.790509355931</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10259,15 +10259,15 @@
       </c>
       <c r="H113" s="44" t="n">
         <f aca="false">H112+H111</f>
-        <v>-210.095167646701</v>
+        <v>-210.040923379036</v>
       </c>
       <c r="I113" s="44" t="n">
         <f aca="false">I112+I111</f>
-        <v>-359.882446244934</v>
+        <v>-359.790509355931</v>
       </c>
       <c r="J113" s="44" t="n">
         <f aca="false">J112+J111</f>
-        <v>-483.794438638808</v>
+        <v>-483.684855011667</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10375,15 +10375,15 @@
       </c>
       <c r="H118" s="28" t="n">
         <f aca="false">H97+H117+H109</f>
-        <v>-210.584167646701</v>
+        <v>-210.529923379036</v>
       </c>
       <c r="I118" s="28" t="n">
         <f aca="false">I97+I117+I109</f>
-        <v>-78.0700585982335</v>
+        <v>-78.0323659768951</v>
       </c>
       <c r="J118" s="28" t="n">
         <f aca="false">J97+J117+J109</f>
-        <v>-50.7604279938735</v>
+        <v>-50.7427812557359</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11041,15 +11041,15 @@
       </c>
       <c r="H146" s="28" t="n">
         <f aca="false">-(G66+G71)*H42/G42</f>
-        <v>463.06036499766</v>
+        <v>463.723383247543</v>
       </c>
       <c r="I146" s="28" t="n">
         <f aca="false">-(H66+H71)*I42/H42</f>
-        <v>476.95217594759</v>
+        <v>478.30978474497</v>
       </c>
       <c r="J146" s="28" t="n">
         <f aca="false">-(I66+I71)*J42/I42</f>
-        <v>490.84398689752</v>
+        <v>492.896186242396</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11062,11 +11062,11 @@
       </c>
       <c r="I147" s="28" t="n">
         <f aca="false">H54*Drivers!$D$29</f>
-        <v>72.2798315395414</v>
+        <v>72.3833231165185</v>
       </c>
       <c r="J147" s="28" t="n">
         <f aca="false">I54*Drivers!$E$29</f>
-        <v>74.4482264857277</v>
+        <v>74.660137810014</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11078,15 +11078,15 @@
       </c>
       <c r="H148" s="28" t="n">
         <f aca="false">H54-G54+H147</f>
-        <v>82.3854796443613</v>
+        <v>82.9942536265794</v>
       </c>
       <c r="I148" s="28" t="n">
         <f aca="false">I54-H54+I147</f>
-        <v>85.0350959288722</v>
+        <v>85.7763507253158</v>
       </c>
       <c r="J148" s="28" t="n">
         <f aca="false">J54-I54+J147</f>
-        <v>87.2034908750585</v>
+        <v>88.0531654188115</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11098,15 +11098,15 @@
       </c>
       <c r="H149" s="28" t="n">
         <f aca="false">-(G66+G71)+H148-H146</f>
-        <v>69.125114646701</v>
+        <v>69.070870379036</v>
       </c>
       <c r="I149" s="28" t="n">
         <f aca="false">-(H66+H71)+I148-I146</f>
-        <v>71.1432849789424</v>
+        <v>71.1899492278895</v>
       </c>
       <c r="J149" s="28" t="n">
         <f aca="false">-(I66+I71)+J148-J146</f>
-        <v>73.3116799251287</v>
+        <v>73.4667639213851</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11119,11 +11119,11 @@
       </c>
       <c r="I150" s="28" t="n">
         <f aca="false">-(H66+H71)*Drivers!$D$30</f>
-        <v>18.0593542349088</v>
+        <v>18.0852119466542</v>
       </c>
       <c r="J150" s="28" t="n">
         <f aca="false">-(I66+I71)*Drivers!$E$30</f>
-        <v>18.601134861956</v>
+        <v>18.6540816050538</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11408,31 +11408,31 @@
         <v>335</v>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="D7" s="31" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G7" s="31" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="J7" s="31" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="K7" s="31" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>336</v>
